--- a/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,6931 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>vJqPCEPP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dOWuRZlo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>schuhen marcel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>E9apS1Bg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>riedel clemens</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>foHTTSAq</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gjasula klaus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MVVlcIlh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>vukotic aleksandar</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6VRnUvLl</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>lopez sergio</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>GbIogcRb</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>klefisch kai</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>rZoUaqpe</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>will paul</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>QHwCPXNM</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>nurnberger fabian</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>nFpZ4rdg</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>bader matthias</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>O2dfXz1S</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>marseiler luca</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>dMPH2dRF</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vilhelmsson oscar</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>IJQn20qM</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>kastenmeier florian</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>bDD84LZO</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>zimmermann matthias</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>llF3GFBo</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hoffmann andre</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>nB0nG58b</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>oberdorf tim</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>OrOFQncs</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>iyoha emmanuel</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>4lYAoXQu</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>tanaka ao</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>WIZ6iQEQ</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>klaus felix</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>xtsqO2z0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>johannesson isak</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>pnf2rSQi</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>sobottka marcel</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>AkoZzyHG</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>appelkamp shinta</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>bDFC7UGu</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>el idrissi othmane</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4ttlRMFN</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>hornby fraser</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2wOM3Nuj</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>kempe tobias</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>hAGrRnhD</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>lakenmacher fynn</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>EBWgEtZc</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>maglica matej</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>80E6DP7t</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>muller andreas</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>x8LSZTrk</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>niemczycki karol</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0zdchsQJ</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>papela merveille</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Qu2qgtqJ</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>zimmermann christoph</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>zLNzuz1T</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>affo karim</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>xOXZ2PxR</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>jastrzembski dennis</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>I7B78NeJ</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>kwasigroch robert</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>YV51rANA</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>quarshie joshua</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>drjyUsZH</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>suso sima</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>h6EmA08j</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>uchino takashi</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>4ttlRMFN</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>hornby fraser</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>4ttlRMFN</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>hornby fraser</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>O2dfXz1S</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>marseiler luca</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>0zdchsQJ</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>papela merveille</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>0zdchsQJ</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>papela merveille</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>nFpZ4rdg</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>bader matthias</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>hAGrRnhD</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>lakenmacher fynn</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>hAGrRnhD</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>lakenmacher fynn</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>foHTTSAq</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>gjasula klaus</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>bDFC7UGu</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>el idrissi othmane</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>bDFC7UGu</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>el idrissi othmane</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>GbIogcRb</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>klefisch kai</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>2wOM3Nuj</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>kempe tobias</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>2wOM3Nuj</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>kempe tobias</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>dMPH2dRF</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>vilhelmsson oscar</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>YV51rANA</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>quarshie joshua</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>YV51rANA</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>quarshie joshua</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>llF3GFBo</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>hoffmann andre</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>AkoZzyHG</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>appelkamp shinta</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>WIZ6iQEQ</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>klaus felix</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>drjyUsZH</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>suso sima</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>drjyUsZH</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>suso sima</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>OrOFQncs</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>iyoha emmanuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2Hl43AnC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4lDmOHX5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>noll nahuel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>p4gsU4KB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>meyerhofer marco</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UyDYD39g</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>jung gideon</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MklWx3Ju</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>itter gian luca</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SpbhoTNS</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>asta simon</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4ftxGNHd</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>muller philipp</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>63Z1rP3l</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>green julian</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>E1IiAd0j</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>massimo roberto</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Kr5mFJ31</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>hrgota branimir</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>p6v39OGe</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>srbeny dennis</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>jkXw3ddG</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>futkeu noel</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>xbHTqKPs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>schenk johannes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>pC5Aa7Fa</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>ter horst jano</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Ik1ykn3o</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>koulis niko</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>COALarg5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>frenkert lukas</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2VV3mWal</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>kirkeskov mikkel</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>GdTT8aB4</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>mees joshua</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tMs28wMD</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>hendrix jorrit</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>joxYnHwl</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>bazzoli luca</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>febm46cJ</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>lorenz marc</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>S4Gl9sVD</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>batmaz malik</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0jQoFve6</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>grodowski joel</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Grp8cIEl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>korber nils</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>INqpznVj</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>mhamdi oualid</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>x6zn4GUo</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>michalski damian</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>rHQfYOz6</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>mustapha suliman</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>GMeZlrII</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>popp leander</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>jLRGx0gk</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>wagner matti</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>dEikH1Kb</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>behrens morten</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>b5ojgUKT</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>bolay luca</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>6uG68W6m</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>bouchama yassine</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>W629DD2p</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>peatow torge</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>GfxLwyRf</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>schad dominik</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>rHQfYOz6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>mustapha suliman</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>rHQfYOz6</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>mustapha suliman</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>p6v39OGe</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>srbeny dennis</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>4ftxGNHd</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>muller philipp</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>E1IiAd0j</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>massimo roberto</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>INqpznVj</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>mhamdi oualid</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>INqpznVj</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>mhamdi oualid</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>jkXw3ddG</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>futkeu noel</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>p4gsU4KB</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>meyerhofer marco</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>0jQoFve6</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>grodowski joel</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>tMs28wMD</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>hendrix jorrit</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>GfxLwyRf</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>schad dominik</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>GfxLwyRf</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>schad dominik</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>pC5Aa7Fa</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>ter horst jano</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>joxYnHwl</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>bazzoli luca</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>SIOxI915</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hWgi894t</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ortag christian</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AeFBlVAF</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gaal tom</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pQtfFS0b</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>reichert johannes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>tzVe0ks3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>strompf philipp</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dv6ASA22</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>allgeier bastian</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KdIMFRBK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>maier philipp</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vRf1i1uQ</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>brandt max</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CCQ1XnWk</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>roesch romario</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Igom1Hq7</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>chessa dennis</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>zZzHBoll</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>keller aaron</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>xhJCltvh</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>higl felix</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>d0rCJ6XA</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>krahl julian</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>lIkG4xvp</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>zimmer jean</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>YyIyM2ke</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>elvedi jan</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0fO4CaGi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>heuer jannis</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>8d13nxU4</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>wekesser erik</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2mMIA66I</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kaloc filip</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>EecfGnDI</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>tomiak boris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>j3uLBTA8</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>ritter marlon</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>WYIHibUi</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tachie richmond</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>843k6G9D</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>hanslik daniel</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>vsimiktN</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>opoku aaron</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>tYi02Be9</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>geyer thomas</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>biFABo7b</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>hyrylainen luka</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>h4kxWnHJ</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>kolbe niklas</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>QDlMCo6E</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>krattenmacher maurice</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>xxmPNHln</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>meier jonathan</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>WYsZC6xm</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>seybold marvin</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Eu3z7RfU</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>stoll lennart</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>AqJh2aZt</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>telalovic semir</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>IysDfUb2</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>ulrich laurin</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>vFfAK508</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>abiama dickson</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>4xOWuCxn</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>afeez aremu</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>rwtqk3Wo</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>kleinhansl florian</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>tddjZy0T</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>klement phillipp</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>YJ7XkHc6</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>robinson leon</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>CdGwhV3n</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>spahic avdo</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>QDlMCo6E</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>krattenmacher maurice</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>QDlMCo6E</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>krattenmacher maurice</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>zZzHBoll</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>keller aaron</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>xxmPNHln</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>meier jonathan</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>xxmPNHln</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>meier jonathan</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>Igom1Hq7</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>chessa dennis</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>biFABo7b</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>hyrylainen luka</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>biFABo7b</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>hyrylainen luka</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>vRf1i1uQ</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>brandt max</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>AqJh2aZt</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>telalovic semir</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>AqJh2aZt</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>telalovic semir</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>xhJCltvh</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>higl felix</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>vFfAK508</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>abiama dickson</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>vFfAK508</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>abiama dickson</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>WYIHibUi</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>tachie richmond</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>2mMIA66I</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>kaloc filip</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>lIkG4xvp</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>zimmer jean</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>vsimiktN</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>opoku aaron</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>YJ7XkHc6</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>robinson leon</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>YJ7XkHc6</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>robinson leon</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>j3uLBTA8</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>ritter marlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EeIMLi2t</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AJxwkipQ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>heekeren justin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ddk0fpFO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>gantenbein adrian</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2RkZAE6q</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kalas tomas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>fDRz02r7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>schallenberg ron</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EPljTOtA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>murkin derry john</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4vZGRgLG</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>seguin paul</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>nwBJRX3k</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>bachmann janik</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>YVGPu1iB</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>aydin mehmet can</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Cxnyxxgo</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>karaman kenan</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>rD62a0HL</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>mohr tobias</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>OUIcAVnP</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>sylla moussa</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>lIF2ygN5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>grill lennart</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>buoGx5As</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ehlers kevin</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0jwc2VzN</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>bicakcic ermin</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>GrOfIBN6</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>nikolaou jannis</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>8EefHxEo</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>ba sanoussy</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>tObbOJVL</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>kohler sven</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>MByrUjOa</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>bell bell leon</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>4lY0fSsi</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>kaufmann fabio</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>4hqPiSrL</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>raebiger sidney</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>zLS8H4GJ</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>gomez johan</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Y3tQC4Xd</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>philippe rayan</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Wfl5qKf9</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>cisse ibrahima</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>4voxenxD</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>donkor anton leander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>6DQejPXt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>hoffmann ron thorben</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>00CSnIud</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>hojlund emil</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>6DV32J3r</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>kaminski marcin</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>nHQOxHTR</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>matriciani henning</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>tblOaBDU</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>polter sebastian</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>vwzPuSdM</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>sanchez felipe</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>4InA4HVE</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>wasinski martin</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>hKBLR8mG</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>conteh christian</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>6FWxDXx1</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>di michele sanchez fabio</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>bmUbcbyD</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>duda justin</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>SrufAa0j</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>ivanov robert</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>zi5iH5J2</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>krausse robin</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>ENugzypi</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ould chikh walid</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>WQn9uy89</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>rittmuller marvin</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>44GKzvqF</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>szabo levente</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>46PKSB4h</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>tauer niklas</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>4voxenxD</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>donkor anton leander</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>4voxenxD</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>donkor anton leander</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>YVGPu1iB</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>aydin mehmet can</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>6DV32J3r</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>kaminski marcin</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>6DV32J3r</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>kaminski marcin</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>nwBJRX3k</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>bachmann janik</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>00CSnIud</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>hojlund emil</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>00CSnIud</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>hojlund emil</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>rD62a0HL</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>mohr tobias</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>tblOaBDU</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>polter sebastian</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>tblOaBDU</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>polter sebastian</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>Cxnyxxgo</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>karaman kenan</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>Wfl5qKf9</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>cisse ibrahima</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>Wfl5qKf9</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>cisse ibrahima</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2RkZAE6q</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>kalas tomas</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>44GKzvqF</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>szabo levente</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>44GKzvqF</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>szabo levente</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>4hqPiSrL</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>raebiger sidney</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>6FWxDXx1</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>di michele sanchez fabio</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>6FWxDXx1</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>di michele sanchez fabio</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>MByrUjOa</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>bell bell leon</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>hKBLR8mG</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>conteh christian</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>hKBLR8mG</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>conteh christian</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>buoGx5As</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>ehlers kevin</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>ENugzypi</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>ould chikh walid</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>ENugzypi</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>ould chikh walid</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>4lY0fSsi</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>kaufmann fabio</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>SrufAa0j</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>ivanov robert</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>SrufAa0j</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>ivanov robert</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>Y3tQC4Xd</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>philippe rayan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>fiod5WHa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pGbfkpdp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>zieler ron robert</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pbQe8KLk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>neumann phil</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>M905oPyB</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>halstenberg marcel</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>jXbmuyxr</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>knight josh</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>EwiNuF2j</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>muroya sei</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MHCUmJt8</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>leopold enzo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>hGTaHOb3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>kunze fabian</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>I5L7U2jR</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>dehm jannik</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Wz91fbh7</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>nielsen havard</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>K8fS4hgT</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rochelt jannik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>nuJC7uWq</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>tresoldi nicolo</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S61OwR4A</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>gebhardt felix</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>CGE2sm8F</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>saller benedikt</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>pdibd5af</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ballas florian</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>fJ7n0LTa</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>breunig louis</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>n7CbWHO8</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>hein bryan</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gt5Hjtif</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>geipl andreas</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>GIIxXLKM</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>ernst sebastian</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2ksQjZTe</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>proger kai</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>I7rPshxq</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>viet christian</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>jFJHrLbo</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>kother dominik</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>lKXHsLEd</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>husseyn chakroun</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2qfaierQ</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>christiansen max</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>z7yOJYMd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ezeh brooklyn</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Eg3YK4MG</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>gindorf lars</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>8ljKAJPh</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>lee hyun ju</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>UmXoNi4H</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>ngankam jessic</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>Sz9Ehva5</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>uhlmann eric</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>AyEI4rkI</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>voglsammer andreas</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>6mRlSO05</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>weinkauf leo</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2794IiQ0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>bauer jonas</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>EPcoFv36</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>bittroff alexander</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>EBumrDsB</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>galjen dejan</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>xC6qCyA1</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>meyer max</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>dxi8kT74</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>ouro tagba mansour</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>6qXZFscl</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>pollersbeck julian</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>AyEI4rkI</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>voglsammer andreas</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>AyEI4rkI</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>voglsammer andreas</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>Wz91fbh7</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>nielsen havard</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>Eg3YK4MG</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>gindorf lars</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>Eg3YK4MG</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>gindorf lars</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>K8fS4hgT</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>rochelt jannik</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>2qfaierQ</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>christiansen max</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>2qfaierQ</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>christiansen max</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>hGTaHOb3</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>kunze fabian</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>UmXoNi4H</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>ngankam jessic</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>UmXoNi4H</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>ngankam jessic</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>nuJC7uWq</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>tresoldi nicolo</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>z7yOJYMd</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>ezeh brooklyn</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>z7yOJYMd</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>ezeh brooklyn</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>EwiNuF2j</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>muroya sei</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>Gt5Hjtif</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>geipl andreas</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>dxi8kT74</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>ouro tagba mansour</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>dxi8kT74</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>ouro tagba mansour</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>jFJHrLbo</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>kother dominik</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>EBumrDsB</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>galjen dejan</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>EBumrDsB</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>galjen dejan</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>CGE2sm8F</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>saller benedikt</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>GIIxXLKM</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>ernst sebastian</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>OWxD1lHO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tbbK5T30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ernst tjark</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Slhuy0y3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>kenny jonjoe</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>A5MUk7uC</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>gechter linus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AR2PqO6h</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>kempf marc oliver</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pOJNR06U</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>dudziak jeremy</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6XydaRuI</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>demme diego</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>G6KuK9GH</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>winkler marten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>QNd9XJHR</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>cuisance mickael</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>zPa6aAD8</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>maza ibrahim</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>hWXQwRg8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>dardai palko</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Asecu8a3</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>tabakovic haris</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>SIcKaTOB</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>boevink pelle</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>pWddyVUm</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>scheller tjark</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>dzo2WHvU</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>gotze felix</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>8SBmrZDU</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>musliu visar</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>6LxWRuTN</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>obermair raphael</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>UifTyptK</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>castaneda santiago</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>vi6EGzsg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>klaas sebastian</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>bFUJUT6m</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>zehnter aaron</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>QokFiTR8</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>bilbija filip</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>YLiTuiH4</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>kostons koen</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>8IGkfX37</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>michel sven</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>4fsvgxKi</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>dardai marton</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>pWc1VLFr</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>gersbeck marius</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>fZjqy5kN</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>karbownik michal</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>z1kXPVQh</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>klemens pascal</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>MkyFE8Cj</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>leistner toni</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>txGA3Xvc</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>niederlechner florian</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>jRG1UH32</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>scherhant derry</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>fwLe2Csr</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>schuler luca</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>A7bJsd2S</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>zeefuik deyoraiso</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>AZoyGpY6</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>ansah ilyas</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>Wdl4GSQq</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>baur mika</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>IeGgs0lI</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>curda laurin</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Qa3Y6pbD</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>ens martin</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>fotXcvNj</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>grimaldi adriano</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>rZJgdEKO</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>herrmann luca</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>M5YACtHt</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>hoffmeier marcel</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>2qCKV2dB</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>kinsombi david</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>McI7R28H</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>schubert markus</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>4fsvgxKi</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>dardai marton</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>4fsvgxKi</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>dardai marton</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>AR2PqO6h</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>kempf marc oliver</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>jRG1UH32</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>scherhant derry</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>jRG1UH32</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>scherhant derry</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>hWXQwRg8</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>dardai palko</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>fwLe2Csr</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>schuler luca</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>fwLe2Csr</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>schuler luca</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>G6KuK9GH</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>winkler marten</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>fZjqy5kN</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>karbownik michal</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>fZjqy5kN</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>karbownik michal</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>pOJNR06U</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>dudziak jeremy</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>rZJgdEKO</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>herrmann luca</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>rZJgdEKO</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>herrmann luca</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>vi6EGzsg</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>klaas sebastian</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>fotXcvNj</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>grimaldi adriano</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>fotXcvNj</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>grimaldi adriano</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>YLiTuiH4</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>kostons koen</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>AZoyGpY6</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>ansah ilyas</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>AZoyGpY6</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>ansah ilyas</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>QokFiTR8</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>bilbija filip</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>2qCKV2dB</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>kinsombi david</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>2qCKV2dB</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>kinsombi david</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>8IGkfX37</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>michel sven</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+      <c r="EK7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zkVf7hmm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2LzwmImr</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>weiss max</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fqw6h4xG</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>jung sebastian</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>25frKUlT</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>franke marcel</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>I7SX0eGc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>beifus marcel</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>GIAzln7R</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>gunther lasse</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>M906HZgc</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rapp nicolai</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>40zt37bl</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>burnic dzenis</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>bDSMzQxh</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>jensen leon</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>EDMSe93h</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wanitzek marvin</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SbT0RqHT</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>zivzivadze budu</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>pKBTHk4J</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>schleusener fabian</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>bylmonK5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>reichert jan</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>IDLXfI9o</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>hofmann jannik</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>4GFyNBT2</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>jeltsch finn</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>AaXC2DTB</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>knoche robin</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Y1uqqiIe</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>soares danilo</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>YeWnSuDP</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>okunuki kanji</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>hnqDstcS</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>castrop jens</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>I1JWh0I4</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>flick florian</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>zsLgxeCo</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>jander caspar</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>lURc3Lpo</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>pick florian</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>rHUQL532</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>schleimer lukas</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>tCukSZJp</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>conte bambase</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>W8QSb5W7</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>ersungur ali eren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>SblF0Ls2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>geller robert</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>YmxBM18O</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>herold david</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>ncJb7S2p</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>heusser robin</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>GQfeRwRt</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>himmelmann robin</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Y931ivlJ</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>hunziker andrin</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>AuKINlFp</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>kobald christopher</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>za6eaoT4</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>pinto pedrosa rafael</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>CYhM4Z9N</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>forkel dustin</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>razRw7r9</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>joachims simon</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>QPegJQ59</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>mathenia christian</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>QszFtnum</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>seidel nick</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>Sj1nU4Ob</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>serra janni luca</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>UNcy9ySd</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>sevcik michal</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>l4haZLZ5</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>valentini enrico</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>YmxBM18O</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>herold david</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>YmxBM18O</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>herold david</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>GIAzln7R</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>gunther lasse</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>tCukSZJp</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>conte bambase</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>tCukSZJp</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>conte bambase</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>40zt37bl</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>burnic dzenis</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>Y931ivlJ</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>hunziker andrin</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>Y931ivlJ</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>hunziker andrin</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>pKBTHk4J</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>schleusener fabian</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>ncJb7S2p</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>heusser robin</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>ncJb7S2p</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>heusser robin</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>bDSMzQxh</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>jensen leon</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>W8QSb5W7</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>ersungur ali eren</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>W8QSb5W7</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>ersungur ali eren</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>SbT0RqHT</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>zivzivadze budu</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>YeWnSuDP</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>okunuki kanji</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>l4haZLZ5</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>valentini enrico</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>l4haZLZ5</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>valentini enrico</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>IDLXfI9o</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>hofmann jannik</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>CYhM4Z9N</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>forkel dustin</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>CYhM4Z9N</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>forkel dustin</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>hnqDstcS</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>castrop jens</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>AaXC2DTB</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>knoche robin</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>Sj1nU4Ob</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>serra janni luca</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>Sj1nU4Ob</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>serra janni luca</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>rHUQL532</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>schleimer lukas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>f5QUJVWh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dWQIRGp0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>reimann dominik</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>nT3WIdHQ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hugonet jean</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>EsnjdRBb</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>mathisen marcus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dClubWya</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>heber daniel</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AVw9NxQp</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>el hankouri mohammed</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>fH72vUIc</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gnaka silas</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Kr4UWDeF</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>omer el zein abu bekir</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>xA8O15U4</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>musonda lubambo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>hjh8FYxE</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>teixera bryan</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>xnYgdAQ0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>kaars martijn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>UgcDv2mo</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>burcu livan</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Kz0IYO5q</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>kristof nicolas</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Sr0pRlmi</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>baum elias</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>CADMRt26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>pinckert lukas</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>nkVANHYO</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>le joncour florian</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>MmRiKDc4</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>neubauer maurice</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>UN7i7Cf3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>fellhauer robin</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>bN5KbyQf</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>sahin semih</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Kv8zt49I</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>stock paul</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>8S91z1hc</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>feil manuel</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>CSvc98Io</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>schnellbacher luca pascal</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>r39piUjr</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>bockhorn herbert</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>MolPXmrg</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>ceka jason</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>IiYd3b4I</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>hercher philipp</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>A9kiVOrq</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>hoti andi</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>EkMrawol</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>ito tatsuya</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>pEQYX0TC</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>krempicki connor</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>QLxRGC6m</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>kruth noah</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>lldT3gXT</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>marusic aleksa</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>QVb7v3D2</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>muller tobias</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>WSuIj5OD</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>boss tim</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>EPKIUO4H</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>boyamba joseph</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>hvpnPMDt</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>durholtz luca</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>CrYn57el</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>mahmoud mohammad</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>vDGKu2dd</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>pantschenko daniel</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>fHsspqLg</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>sicker arne</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>IiYd3b4I</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>hercher philipp</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>IiYd3b4I</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>hercher philipp</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>AVw9NxQp</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>el hankouri mohammed</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>EkMrawol</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>ito tatsuya</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>EkMrawol</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>ito tatsuya</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>UgcDv2mo</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>burcu livan</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>lldT3gXT</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>marusic aleksa</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>lldT3gXT</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>marusic aleksa</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>Kr4UWDeF</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>omer el zein abu bekir</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>MolPXmrg</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>ceka jason</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>MolPXmrg</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>ceka jason</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>hjh8FYxE</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>teixera bryan</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>hvpnPMDt</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>durholtz luca</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>hvpnPMDt</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>durholtz luca</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>8S91z1hc</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>feil manuel</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>CSvc98Io</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>schnellbacher luca pascal</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>Kv8zt49I</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>stock paul</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OA1xkBXI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6TJsuRSF</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>urbig jonas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sb7k5TPr</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>thielmann jan</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>QPixSkoq</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hubers timo</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bXZbYU0M</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pauli julian</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>rewP99L4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>paqarada leart</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>pOwJWWP0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>martel eric</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>j5EdhX7Q</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ljubicic dejan</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>G2QyHRP1</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>denis huseinbasic</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>UJH9L4T5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>waldschmidt gian luca</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2g6lypL5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>downs damion</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>OYG8XB8m</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>lemperle tim</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Mcx5TeXa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>heuer fernandes daniel</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0I86Dos5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>jatta bakery</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>jV3UcfqE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hadzikadunic dennis</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>f1yi2OxU</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>schonlau bastian</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>bympdcHJ</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>muheim miro</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>6LrWuvC1</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>elfadli daniel</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>MRT6G9pQ</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>meffert jonas</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Kf9h2WGQ</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>reis ludovit</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>SClyr2eG</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>karabec adam</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>SllmjqTg</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>konigsdorffer ransford</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>GOw3GAue</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>dompe jean luc</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>6JByionA</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>adamyan sargis</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>4hGyTe7N</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>carstensen rasmus</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>ET08RjhJ</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>dietz florian</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>Gr2FbER2</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>heintz dominique</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>EsYIPmhj</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>maina linton</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4UathafT</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>obuz marvin</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>nmOIHA5M</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>olesen mathias</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>zksQHtJm</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>pentke philipp</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>vPWVYzsB</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>waschenbach meiko</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>OIB9EK1N</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>balde fabio</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>IJvNR7LH</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>heyer moritz</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>UBu3UwYC</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>katterbach noah</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>r7AcmFSk</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>mickel tom</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>OG4M49Jf</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>mikelbrencis william</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>f59jliZi</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>oztunali levin</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>WQz3HTDf</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>pherai manuel</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>UcheHrHf</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>ramos guilherme</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>E7JLI2DO</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>selke davie</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>EsYIPmhj</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>maina linton</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>EsYIPmhj</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>maina linton</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>UJH9L4T5</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>waldschmidt gian luca</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>6JByionA</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>adamyan sargis</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>6JByionA</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>adamyan sargis</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>2g6lypL5</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>downs damion</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>ET08RjhJ</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>dietz florian</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>ET08RjhJ</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>dietz florian</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>OYG8XB8m</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>lemperle tim</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>4UathafT</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>obuz marvin</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>4UathafT</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>obuz marvin</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>G2QyHRP1</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>denis huseinbasic</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>Gr2FbER2</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>heintz dominique</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>Gr2FbER2</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>heintz dominique</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>bXZbYU0M</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>pauli julian</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>f59jliZi</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>oztunali levin</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>f59jliZi</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>oztunali levin</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>SClyr2eG</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>karabec adam</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>OIB9EK1N</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>balde fabio</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>OIB9EK1N</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>balde fabio</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>GOw3GAue</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>dompe jean luc</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>IJvNR7LH</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>heyer moritz</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>IJvNR7LH</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>heyer moritz</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>Kf9h2WGQ</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>reis ludovit</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>E7JLI2DO</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>selke davie</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>E7JLI2DO</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>selke davie</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>SllmjqTg</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>konigsdorffer ransford</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>OG4M49Jf</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>mikelbrencis william</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>OG4M49Jf</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>mikelbrencis william</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>0I86Dos5</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>jatta bakery</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,4047 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>IViLLjPF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IJQn20qM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>kastenmeier florian</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bDD84LZO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>zimmermann matthias</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>llF3GFBo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>hoffmann andre</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nB0nG58b</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>oberdorf tim</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OrOFQncs</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>iyoha emmanuel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4lYAoXQu</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tanaka ao</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>WIZ6iQEQ</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>klaus felix</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>pnf2rSQi</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>sobottka marcel</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>xtsqO2z0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>johannesson isak</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AkoZzyHG</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>appelkamp shinta</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2LzwmImr</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>weiss max</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>fqw6h4xG</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>jung sebastian</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>25frKUlT</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>franke marcel</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>I7SX0eGc</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>beifus marcel</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GIAzln7R</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>gunther lasse</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>M906HZgc</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>rapp nicolai</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bDSMzQxh</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>jensen leon</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>40zt37bl</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>burnic dzenis</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>EDMSe93h</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>wanitzek marvin</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>pKBTHk4J</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>schleusener fabian</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>SbT0RqHT</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>zivzivadze budu</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>zLNzuz1T</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>affo karim</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>xOXZ2PxR</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>jastrzembski dennis</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>I7B78NeJ</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>kwasigroch robert</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>YV51rANA</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>quarshie joshua</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>drjyUsZH</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>suso sima</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>tCukSZJp</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>conte bambase</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>W8QSb5W7</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>ersungur ali eren</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>SblF0Ls2</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>geller robert</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>YmxBM18O</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>herold david</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>ncJb7S2p</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>heusser robin</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>GQfeRwRt</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>himmelmann robin</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>Y931ivlJ</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>hunziker andrin</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>AuKINlFp</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>kobald christopher</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>za6eaoT4</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>pinto pedrosa rafael</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>AkoZzyHG</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>appelkamp shinta</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>pnf2rSQi</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>sobottka marcel</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Y931ivlJ</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>hunziker andrin</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Y931ivlJ</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>hunziker andrin</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>pKBTHk4J</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>schleusener fabian</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>tCukSZJp</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>conte bambase</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>tCukSZJp</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>conte bambase</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>40zt37bl</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>burnic dzenis</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>YmxBM18O</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>herold david</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>YmxBM18O</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>herold david</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>GIAzln7R</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>gunther lasse</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>ncJb7S2p</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>heusser robin</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>ncJb7S2p</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>heusser robin</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>SbT0RqHT</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>zivzivadze budu</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>tC1Aa08D</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kz0IYO5q</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kristof nicolas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sr0pRlmi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>baum elias</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CADMRt26</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pinckert lukas</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nkVANHYO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>le joncour florian</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MmRiKDc4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>neubauer maurice</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CSvc98Io</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>schnellbacher luca pascal</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UN7i7Cf3</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>fellhauer robin</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>bN5KbyQf</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>sahin semih</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Kv8zt49I</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>stock paul</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>8S91z1hc</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>feil manuel</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6TJsuRSF</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>urbig jonas</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Sb7k5TPr</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>thielmann jan</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>QPixSkoq</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hubers timo</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Gr2FbER2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>heintz dominique</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>rewP99L4</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>paqarada leart</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>pOwJWWP0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>martel eric</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>j5EdhX7Q</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>ljubicic dejan</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>G2QyHRP1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>denis huseinbasic</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>EsYIPmhj</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>maina linton</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2g6lypL5</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>downs damion</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>OYG8XB8m</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>lemperle tim</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>WSuIj5OD</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>boss tim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>EPKIUO4H</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>boyamba joseph</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>hvpnPMDt</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>durholtz luca</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>CrYn57el</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>mahmoud mohammad</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>vDGKu2dd</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>pantschenko daniel</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>fHsspqLg</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>sicker arne</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>6JByionA</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>adamyan sargis</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>4hGyTe7N</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>carstensen rasmus</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>ET08RjhJ</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>dietz florian</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>nmOIHA5M</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>olesen mathias</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>bXZbYU0M</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>pauli julian</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>zksQHtJm</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>pentke philipp</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>29mHF4BE</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>tigges steffen</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>CzbQqKcT</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>uth mark</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>UJH9L4T5</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>waldschmidt gian luca</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>CSvc98Io</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>schnellbacher luca pascal</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>Kv8zt49I</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>stock paul</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>CrYn57el</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>mahmoud mohammad</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>CrYn57el</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>mahmoud mohammad</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>CzbQqKcT</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>uth mark</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>CzbQqKcT</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>uth mark</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>2g6lypL5</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>downs damion</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>UJH9L4T5</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>waldschmidt gian luca</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>UJH9L4T5</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>waldschmidt gian luca</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>CzbQqKcT</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>uth mark</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>ET08RjhJ</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>dietz florian</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>ET08RjhJ</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>dietz florian</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>EsYIPmhj</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>maina linton</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>bXZbYU0M</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>pauli julian</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>bXZbYU0M</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>pauli julian</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>Gr2FbER2</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>heintz dominique</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>8S91z1hc</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>feil manuel</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>29mHF4BE</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>tigges steffen</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>29mHF4BE</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>tigges steffen</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>OYG8XB8m</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>lemperle tim</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>YJ3eN30K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>bylmonK5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>reichert jan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IDLXfI9o</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hofmann jannik</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4GFyNBT2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>jeltsch finn</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AaXC2DTB</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>knoche robin</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Y1uqqiIe</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>soares danilo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>YeWnSuDP</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>okunuki kanji</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>hnqDstcS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>castrop jens</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>I1JWh0I4</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>flick florian</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>zsLgxeCo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>jander caspar</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>lURc3Lpo</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>pick florian</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>rHUQL532</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>schleimer lukas</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>AJxwkipQ</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>heekeren justin</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ddk0fpFO</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>gantenbein adrian</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Wfl5qKf9</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>cisse ibrahima</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>6DV32J3r</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>kaminski marcin</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>EPljTOtA</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>murkin derry john</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>fDRz02r7</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>schallenberg ron</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>nwBJRX3k</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>bachmann janik</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>OUIcAVnP</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>sylla moussa</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Cxnyxxgo</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>karaman kenan</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>rD62a0HL</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>mohr tobias</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>00CSnIud</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>hojlund emil</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>CYhM4Z9N</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>forkel dustin</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>YsfI5FfH</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>janisch tim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>fRViBeZ4</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>lubach rafael</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>QPegJQ59</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>mathenia christian</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>QszFtnum</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>seidel nick</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>UNcy9ySd</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>sevcik michal</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>YVGPu1iB</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>aydin mehmet can</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>zyIBok7d</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>bulut taylan</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>4voxenxD</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>donkor anton leander</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>4YlHypVh</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>gruger max</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>6DQejPXt</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>hoffmann ron thorben</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>tblOaBDU</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>polter sebastian</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>vwzPuSdM</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>sanchez felipe</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>4vZGRgLG</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>seguin paul</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>4InA4HVE</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>wasinski martin</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>l4haZLZ5</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>valentini enrico</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>l4haZLZ5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>valentini enrico</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>Y1uqqiIe</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>soares danilo</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>CYhM4Z9N</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>forkel dustin</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>CYhM4Z9N</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>forkel dustin</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>YeWnSuDP</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>okunuki kanji</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>hnqDstcS</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>castrop jens</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>YVGPu1iB</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>aydin mehmet can</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>YVGPu1iB</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>aydin mehmet can</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>00CSnIud</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>hojlund emil</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>4voxenxD</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>donkor anton leander</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>4voxenxD</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>donkor anton leander</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>rD62a0HL</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>mohr tobias</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>l4haZLZ5</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>valentini enrico</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>fRViBeZ4</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>lubach rafael</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>fRViBeZ4</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>lubach rafael</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>lURc3Lpo</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>pick florian</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>YsfI5FfH</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>janisch tim</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>YsfI5FfH</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>janisch tim</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>rHUQL532</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>schleimer lukas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>h4pSHsOs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>d0rCJ6XA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>krahl julian</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lIkG4xvp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>zimmer jean</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>YyIyM2ke</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>elvedi jan</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0fO4CaGi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>heuer jannis</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8d13nxU4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>wekesser erik</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2mMIA66I</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>kaloc filip</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>EecfGnDI</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>tomiak boris</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>j3uLBTA8</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ritter marlon</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>WYIHibUi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>tachie richmond</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>843k6G9D</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>hanslik daniel</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>vsimiktN</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>opoku aaron</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4lDmOHX5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>noll nahuel</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>p4gsU4KB</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>meyerhofer marco</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>UyDYD39g</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>jung gideon</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>MklWx3Ju</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>itter gian luca</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SpbhoTNS</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>asta simon</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>4ftxGNHd</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>muller philipp</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>63Z1rP3l</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>green julian</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>E1IiAd0j</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>massimo roberto</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Kr5mFJ31</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>hrgota branimir</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>p6v39OGe</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>srbeny dennis</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>jkXw3ddG</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>futkeu noel</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>vFfAK508</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>abiama dickson</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>lnwXQmIl</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>ache ragnar</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>rwtqk3Wo</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>kleinhansl florian</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>tddjZy0T</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>klement phillipp</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>YJ7XkHc6</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>robinson leon</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>KdxqdGYD</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>dietz maximilian</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>Grp8cIEl</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>korber nils</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>INqpznVj</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>mhamdi oualid</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>x6zn4GUo</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>michalski damian</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>GMeZlrII</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>popp leander</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>jLRGx0gk</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>wagner matti</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>WYIHibUi</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>tachie richmond</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>lnwXQmIl</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>ache ragnar</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>lnwXQmIl</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>ache ragnar</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>2mMIA66I</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>kaloc filip</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>lIkG4xvp</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>zimmer jean</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>E1IiAd0j</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>massimo roberto</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>KdxqdGYD</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>dietz maximilian</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>KdxqdGYD</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>dietz maximilian</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>p4gsU4KB</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>meyerhofer marco</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>p6v39OGe</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>srbeny dennis</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>GMeZlrII</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>popp leander</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>GMeZlrII</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>popp leander</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>jkXw3ddG</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>futkeu noel</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>CdGwhV3n</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>spahic avdo</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>843k6G9D</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>hanslik daniel</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>x6zn4GUo</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>michalski damian</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>x6zn4GUo</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>michalski damian</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>4ftxGNHd</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>muller philipp</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>StuiCwhJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S61OwR4A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gebhardt felix</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CGE2sm8F</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>saller benedikt</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pdibd5af</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ballas florian</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>fJ7n0LTa</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>breunig louis</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>jcdPxHgs</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>schonfelder oscar</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2ksQjZTe</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>proger kai</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GIIxXLKM</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ernst sebastian</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gt5Hjtif</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>geipl andreas</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>I7rPshxq</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>viet christian</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>jFJHrLbo</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>kother dominik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>jNTX1fbc</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>kuhlwetter christian</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>hWgi894t</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>ortag christian</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>AeFBlVAF</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>gaal tom</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>pQtfFS0b</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>reichert johannes</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>tzVe0ks3</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>strompf philipp</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>dv6ASA22</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>allgeier bastian</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>KdIMFRBK</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>maier philipp</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>vRf1i1uQ</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>brandt max</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>CCQ1XnWk</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>roesch romario</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Igom1Hq7</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>chessa dennis</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>QDlMCo6E</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>krattenmacher maurice</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>xhJCltvh</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>higl felix</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>EPcoFv36</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>bittroff alexander</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>n7CbWHO8</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>hein bryan</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>hSia4qTi</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>ochojski nico</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>dxi8kT74</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>ouro tagba mansour</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>6qXZFscl</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>pollersbeck julian</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>jHaFpGhl</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>castelle niklas horst</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>biFABo7b</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>hyrylainen luka</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>zZzHBoll</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>keller aaron</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>h4kxWnHJ</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>kolbe niklas</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Uk5rXoFR</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>ludwig andreas</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>xxmPNHln</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>meier jonathan</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>WYsZC6xm</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>seybold marvin</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>Eu3z7RfU</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>stoll lennart</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>AqJh2aZt</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>telalovic semir</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>jNTX1fbc</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>kuhlwetter christian</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>Gt5Hjtif</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>geipl andreas</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>jFJHrLbo</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>kother dominik</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>biFABo7b</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>hyrylainen luka</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>biFABo7b</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>hyrylainen luka</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>KdIMFRBK</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>maier philipp</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>h4kxWnHJ</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>kolbe niklas</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>h4kxWnHJ</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>kolbe niklas</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>AeFBlVAF</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>gaal tom</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>zZzHBoll</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>keller aaron</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>zZzHBoll</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>keller aaron</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>CCQ1XnWk</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>roesch romario</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>AqJh2aZt</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>telalovic semir</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>AqJh2aZt</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>telalovic semir</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>Igom1Hq7</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>chessa dennis</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>dxi8kT74</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>ouro tagba mansour</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>dxi8kT74</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>ouro tagba mansour</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>2ksQjZTe</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>proger kai</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>jHaFpGhl</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>castelle niklas horst</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>jHaFpGhl</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>castelle niklas horst</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>QDlMCo6E</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>krattenmacher maurice</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>hSia4qTi</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>ochojski nico</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>hSia4qTi</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>ochojski nico</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>CGE2sm8F</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>saller benedikt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EK6"/>
+  <dimension ref="A1:EK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,3024 +731,3080 @@
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_away_1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_1</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_2</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_2</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_3</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_3</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_4</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_4</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_5</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_5</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_7</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_7</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_8</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_8</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_away_9</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_away_9</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_1</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_1</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_2</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_2</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_3</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_3</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_4</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_4</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_5</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_5</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_6</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_6</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_7</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_7</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_8</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_8</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_9</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_9</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_home_9</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_home_9</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_13</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_13</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_14</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_14</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_15</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IViLLjPF</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IJQn20qM</t>
+          <t>lIF2ygN5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kastenmeier florian</t>
+          <t>grill lennart</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bDD84LZO</t>
+          <t>SrufAa0j</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>zimmermann matthias</t>
+          <t>ivanov robert</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>llF3GFBo</t>
+          <t>0jwc2VzN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hoffmann andre</t>
+          <t>bicakcic ermin</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>nB0nG58b</t>
+          <t>GrOfIBN6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>oberdorf tim</t>
+          <t>nikolaou jannis</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>OrOFQncs</t>
+          <t>WQn9uy89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>iyoha emmanuel</t>
+          <t>rittmuller marvin</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4lYAoXQu</t>
+          <t>4lY0fSsi</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>tanaka ao</t>
+          <t>kaufmann fabio</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>WIZ6iQEQ</t>
+          <t>tObbOJVL</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>klaus felix</t>
+          <t>kohler sven</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>pnf2rSQi</t>
+          <t>6FWxDXx1</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>sobottka marcel</t>
+          <t>di michele sanchez fabio</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>xtsqO2z0</t>
+          <t>zLS8H4GJ</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>johannesson isak</t>
+          <t>gomez johan</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AkoZzyHG</t>
+          <t>Y3tQC4Xd</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>appelkamp shinta</t>
+          <t>philippe rayan</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>nqadvVA9</t>
+          <t>ENugzypi</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>rossmann tim</t>
+          <t>ould chikh walid</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2LzwmImr</t>
+          <t>QqugudYS</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>weiss max</t>
+          <t>trapp kevin</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>fqw6h4xG</t>
+          <t>Ii8pjsY2</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>jung sebastian</t>
+          <t>kristensen rasmus</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>25frKUlT</t>
+          <t>WzSF4nFU</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>franke marcel</t>
+          <t>koch robin</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>I7SX0eGc</t>
+          <t>z9f8RgUQ</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>beifus marcel</t>
+          <t>tuta</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>GIAzln7R</t>
+          <t>t21cpbh2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>gunther lasse</t>
+          <t>nkounkou niels</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>M906HZgc</t>
+          <t>UawLDteR</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>rapp nicolai</t>
+          <t>skhiri ellyes</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>bDSMzQxh</t>
+          <t>K89S36S5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>jensen leon</t>
+          <t>larsson hugo</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>40zt37bl</t>
+          <t>veaF8P5m</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>burnic dzenis</t>
+          <t>gotze mario</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>EDMSe93h</t>
+          <t>44pYRYIC</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>wanitzek marvin</t>
+          <t>marmoush omar</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>pKBTHk4J</t>
+          <t>ltVXPlJU</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>schleusener fabian</t>
+          <t>ekitike hugo</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>SbT0RqHT</t>
+          <t>IusyCIkS</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>zivzivadze budu</t>
+          <t>fares chaibi</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>zLNzuz1T</t>
+          <t>8EefHxEo</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>affo karim</t>
+          <t>ba sanoussy</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>Mkhbm4fo</t>
+          <t>MByrUjOa</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>de wijs jordy</t>
+          <t>bell bell leon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>xOXZ2PxR</t>
+          <t>hKBLR8mG</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>jastrzembski dennis</t>
+          <t>conteh christian</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>I7B78NeJ</t>
+          <t>buoGx5As</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>kwasigroch robert</t>
+          <t>ehlers kevin</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>lvfGmMDJ</t>
+          <t>pS7jnHa8</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>niemiec jonah</t>
+          <t>johansson marko</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>YV51rANA</t>
+          <t>zi5iH5J2</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>quarshie joshua</t>
+          <t>krausse robin</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>CQ7WHnQO</t>
+          <t>4hqPiSrL</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>schmidt danny</t>
+          <t>raebiger sidney</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>drjyUsZH</t>
+          <t>44GKzvqF</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>suso sima</t>
+          <t>szabo levente</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>tCukSZJp</t>
+          <t>46PKSB4h</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>conte bambase</t>
+          <t>tauer niklas</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>W8QSb5W7</t>
+          <t>xtDO40Js</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>ersungur ali eren</t>
+          <t>amenda aurele</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>SblF0Ls2</t>
+          <t>nwlyAsLt</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>geller robert</t>
+          <t>brown nathaniel</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>YmxBM18O</t>
+          <t>0xxsmCo1</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>herold david</t>
+          <t>collins nnamdi</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>ncJb7S2p</t>
+          <t>0daEaUg4</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>heusser robin</t>
+          <t>dina eric</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>GQfeRwRt</t>
+          <t>WWSwmP1d</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>himmelmann robin</t>
+          <t>hojlund oscar</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>Y931ivlJ</t>
+          <t>W4tC13d7</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>hunziker andrin</t>
+          <t>kaua santos</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>AuKINlFp</t>
+          <t>2ebHJb1N</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>kobald christopher</t>
+          <t>knauff ansgar</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>za6eaoT4</t>
+          <t>j5PxPTVi</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>pinto pedrosa rafael</t>
+          <t>matanovic igor</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>lvfGmMDJ</t>
+          <t>hljGyhNr</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>niemiec jonah</t>
+          <t>uzun can yilmaz</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>lvfGmMDJ</t>
+          <t>hKBLR8mG</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>niemiec jonah</t>
+          <t>conteh christian</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>nqadvVA9</t>
+          <t>hKBLR8mG</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>rossmann tim</t>
+          <t>conteh christian</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>CQ7WHnQO</t>
+          <t>4lY0fSsi</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>schmidt danny</t>
+          <t>kaufmann fabio</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>CQ7WHnQO</t>
+          <t>zi5iH5J2</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>schmidt danny</t>
+          <t>krausse robin</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>AkoZzyHG</t>
+          <t>zi5iH5J2</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>appelkamp shinta</t>
+          <t>krausse robin</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>Mkhbm4fo</t>
+          <t>tObbOJVL</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>de wijs jordy</t>
+          <t>kohler sven</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>Mkhbm4fo</t>
+          <t>8EefHxEo</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>de wijs jordy</t>
+          <t>ba sanoussy</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>pnf2rSQi</t>
+          <t>8EefHxEo</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>sobottka marcel</t>
+          <t>ba sanoussy</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>Y931ivlJ</t>
+          <t>WQn9uy89</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>hunziker andrin</t>
+          <t>rittmuller marvin</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>Y931ivlJ</t>
+          <t>46PKSB4h</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>hunziker andrin</t>
+          <t>tauer niklas</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>pKBTHk4J</t>
+          <t>46PKSB4h</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>schleusener fabian</t>
+          <t>tauer niklas</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>tCukSZJp</t>
+          <t>ENugzypi</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>conte bambase</t>
+          <t>ould chikh walid</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>tCukSZJp</t>
+          <t>44GKzvqF</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>conte bambase</t>
+          <t>szabo levente</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>40zt37bl</t>
+          <t>44GKzvqF</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>burnic dzenis</t>
+          <t>szabo levente</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>YmxBM18O</t>
+          <t>Y3tQC4Xd</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>herold david</t>
+          <t>philippe rayan</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>YmxBM18O</t>
+          <t>j5PxPTVi</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>herold david</t>
+          <t>matanovic igor</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>GIAzln7R</t>
+          <t>j5PxPTVi</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>gunther lasse</t>
+          <t>matanovic igor</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>ncJb7S2p</t>
+          <t>ltVXPlJU</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>heusser robin</t>
+          <t>ekitike hugo</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>ncJb7S2p</t>
+          <t>2ebHJb1N</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>heusser robin</t>
+          <t>knauff ansgar</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>SbT0RqHT</t>
+          <t>2ebHJb1N</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>zivzivadze budu</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr"/>
-      <c r="DS2" t="inlineStr"/>
-      <c r="DT2" t="inlineStr"/>
-      <c r="DU2" t="inlineStr"/>
-      <c r="DV2" t="inlineStr"/>
-      <c r="DW2" t="inlineStr"/>
-      <c r="DX2" t="inlineStr"/>
-      <c r="DY2" t="inlineStr"/>
-      <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
-      <c r="EC2" t="inlineStr"/>
-      <c r="ED2" t="inlineStr"/>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="inlineStr"/>
-      <c r="EH2" t="inlineStr"/>
-      <c r="EI2" t="inlineStr"/>
-      <c r="EJ2" t="inlineStr"/>
-      <c r="EK2" t="inlineStr"/>
+          <t>knauff ansgar</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>veaF8P5m</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>gotze mario</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>nwlyAsLt</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>brown nathaniel</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>nwlyAsLt</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>brown nathaniel</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>t21cpbh2</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>nkounkou niels</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>K89S36S5</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>larsson hugo</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>hljGyhNr</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>uzun can yilmaz</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>hljGyhNr</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>uzun can yilmaz</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>IusyCIkS</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>fares chaibi</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tC1Aa08D</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kz0IYO5q</t>
+          <t>pU7xGq1O</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kristof nicolas</t>
+          <t>bethke elias</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sr0pRlmi</t>
+          <t>IinEG7cN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>baum elias</t>
+          <t>rorig henry</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CADMRt26</t>
+          <t>KMBOuGy9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pinckert lukas</t>
+          <t>kusic filip</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>nkVANHYO</t>
+          <t>b1fFcE5O</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>le joncour florian</t>
+          <t>campulka tim</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MmRiKDc4</t>
+          <t>ED0PlhcB</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>neubauer maurice</t>
+          <t>hasse tobias</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CSvc98Io</t>
+          <t>215RGdM4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>schnellbacher luca pascal</t>
+          <t>cigerci tolcay</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>UN7i7Cf3</t>
+          <t>boqVvhP6</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>fellhauer robin</t>
+          <t>juckel janis</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>bN5KbyQf</t>
+          <t>xUfoh7JN</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>sahin semih</t>
+          <t>putze joshua</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Kv8zt49I</t>
+          <t>thMEzwgb</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>stock paul</t>
+          <t>hofmann jonas</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>8S91z1hc</t>
+          <t>lxlccy2F</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>feil manuel</t>
+          <t>halbauer philipp</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>vZBhb9vk</t>
+          <t>ABbxRjdF</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>gerezgiher filimon</t>
+          <t>pronichev maximilian</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>6TJsuRSF</t>
+          <t>ATsadFmo</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>urbig jonas</t>
+          <t>zetterer michael</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Sb7k5TPr</t>
+          <t>xQzNNXkj</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>thielmann jan</t>
+          <t>stark niklas</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>QPixSkoq</t>
+          <t>jacFHyR9</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>hubers timo</t>
+          <t>friedl marco</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Gr2FbER2</t>
+          <t>E7uclPCf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>heintz dominique</t>
+          <t>veljkovic milos</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>rewP99L4</t>
+          <t>tYnkajw9</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>paqarada leart</t>
+          <t>weiser mitchell</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>pOwJWWP0</t>
+          <t>hIljeTIQ</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>martel eric</t>
+          <t>lynen senne</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>j5EdhX7Q</t>
+          <t>jJ1sdqU7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>ljubicic dejan</t>
+          <t>stage jens</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>G2QyHRP1</t>
+          <t>bDdYUcr2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>denis huseinbasic</t>
+          <t>agu felix</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>EsYIPmhj</t>
+          <t>lGA7E78J</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>maina linton</t>
+          <t>schmid romano</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2g6lypL5</t>
+          <t>S6I8rZWk</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>downs damion</t>
+          <t>topp keke</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>OYG8XB8m</t>
+          <t>8McNJcKC</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>lemperle tim</t>
+          <t>ducksch marvin</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>IsoKFb9C</t>
+          <t>v9g6sntb</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>asllani fisnik</t>
+          <t>borgmann axel</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>WSuIj5OD</t>
+          <t>Q3GaVKE6</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>boss tim</t>
+          <t>hajrulla romario</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>EPKIUO4H</t>
+          <t>MFpBCEAk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>boyamba joseph</t>
+          <t>kaizer edgar</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>hvpnPMDt</t>
+          <t>b1AH65fF</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>durholtz luca</t>
+          <t>krauss maximilian</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>CrYn57el</t>
+          <t>WEzRvOGH</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>mahmoud mohammad</t>
+          <t>moker yannik</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>vDGKu2dd</t>
+          <t>6eiNN6an</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>pantschenko daniel</t>
+          <t>oesterhelweg maximilian</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>vqV83aMf</t>
+          <t>p4uscePe</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>schmahl frederik</t>
+          <t>pelivan dominik</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>fHsspqLg</t>
+          <t>xvx2tOOa</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>sicker arne</t>
+          <t>sebald alexander</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>6JByionA</t>
+          <t>0d35x6Et</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>adamyan sargis</t>
+          <t>slamar dennis</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>4hGyTe7N</t>
+          <t>WlEZExcF</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>carstensen rasmus</t>
+          <t>alvero skelly</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>ET08RjhJ</t>
+          <t>AquFxJsn</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>dietz florian</t>
+          <t>backhaus mio</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>nmOIHA5M</t>
+          <t>UNvXGPqn</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>olesen mathias</t>
+          <t>bittencourt leonardo</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>bXZbYU0M</t>
+          <t>2FUXXkKc</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>pauli julian</t>
+          <t>deman olivier</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>zksQHtJm</t>
+          <t>hCB1UCHG</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>pentke philipp</t>
+          <t>grull marco</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>29mHF4BE</t>
+          <t>46r3Wu9b</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>tigges steffen</t>
+          <t>hansen aaroen isak</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>CzbQqKcT</t>
+          <t>xjjdBYsc</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>uth mark</t>
+          <t>jung anthony</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>UJH9L4T5</t>
+          <t>hG2tW3OE</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>waldschmidt gian luca</t>
+          <t>malatini julian</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>IsoKFb9C</t>
+          <t>MkHz7wta</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>asllani fisnik</t>
+          <t>gideon justin</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>IsoKFb9C</t>
+          <t>p4uscePe</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>asllani fisnik</t>
+          <t>pelivan dominik</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>CSvc98Io</t>
+          <t>p4uscePe</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>schnellbacher luca pascal</t>
+          <t>pelivan dominik</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>vqV83aMf</t>
+          <t>xUfoh7JN</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>schmahl frederik</t>
+          <t>putze joshua</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>vqV83aMf</t>
+          <t>0d35x6Et</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>schmahl frederik</t>
+          <t>slamar dennis</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>Kv8zt49I</t>
+          <t>0d35x6Et</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>stock paul</t>
+          <t>slamar dennis</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>CrYn57el</t>
+          <t>b1fFcE5O</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>mahmoud mohammad</t>
+          <t>campulka tim</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>CrYn57el</t>
+          <t>b1AH65fF</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>mahmoud mohammad</t>
+          <t>krauss maximilian</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>vZBhb9vk</t>
+          <t>b1AH65fF</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>gerezgiher filimon</t>
+          <t>krauss maximilian</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>CzbQqKcT</t>
+          <t>lxlccy2F</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>uth mark</t>
+          <t>halbauer philipp</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>CzbQqKcT</t>
+          <t>Q3GaVKE6</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>uth mark</t>
+          <t>hajrulla romario</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>2g6lypL5</t>
+          <t>Q3GaVKE6</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>downs damion</t>
+          <t>hajrulla romario</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>UJH9L4T5</t>
+          <t>ABbxRjdF</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>waldschmidt gian luca</t>
+          <t>pronichev maximilian</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>UJH9L4T5</t>
+          <t>v9g6sntb</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>waldschmidt gian luca</t>
+          <t>borgmann axel</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>CzbQqKcT</t>
+          <t>v9g6sntb</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>uth mark</t>
+          <t>borgmann axel</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>ET08RjhJ</t>
+          <t>boqVvhP6</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>dietz florian</t>
+          <t>juckel janis</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>ET08RjhJ</t>
+          <t>MkHz7wta</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>dietz florian</t>
+          <t>gideon justin</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>EsYIPmhj</t>
+          <t>MkHz7wta</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>maina linton</t>
+          <t>gideon justin</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>bXZbYU0M</t>
+          <t>S6I8rZWk</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>pauli julian</t>
+          <t>topp keke</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>bXZbYU0M</t>
+          <t>xjjdBYsc</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>pauli julian</t>
+          <t>jung anthony</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>Gr2FbER2</t>
+          <t>xjjdBYsc</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>heintz dominique</t>
+          <t>jung anthony</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>rqmHR01A</t>
+          <t>xQzNNXkj</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>sickinger carlo</t>
+          <t>stark niklas</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>rqmHR01A</t>
+          <t>2FUXXkKc</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>sickinger carlo</t>
+          <t>deman olivier</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>rqmHR01A</t>
+          <t>2FUXXkKc</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>sickinger carlo</t>
+          <t>deman olivier</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>8S91z1hc</t>
+          <t>bDdYUcr2</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>feil manuel</t>
+          <t>agu felix</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>29mHF4BE</t>
+          <t>UNvXGPqn</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>tigges steffen</t>
+          <t>bittencourt leonardo</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>29mHF4BE</t>
+          <t>UNvXGPqn</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>tigges steffen</t>
+          <t>bittencourt leonardo</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>OYG8XB8m</t>
+          <t>jJ1sdqU7</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>lemperle tim</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr"/>
-      <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
+          <t>stage jens</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>8McNJcKC</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>ducksch marvin</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YJ3eN30K</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bylmonK5</t>
+          <t>pGtkOYKi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>reichert jan</t>
+          <t>brinkies johannes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IDLXfI9o</t>
+          <t>dn5txvff</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hofmann jannik</t>
+          <t>giesel vincent moreno</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4GFyNBT2</t>
+          <t>KMsZbKZT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>jeltsch finn</t>
+          <t>knothe noel</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AaXC2DTB</t>
+          <t>Gjjy2nL3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>knoche robin</t>
+          <t>sorge alexander</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Y1uqqiIe</t>
+          <t>Wvv0ZPIm</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>soares danilo</t>
+          <t>marcos ronny</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>YeWnSuDP</t>
+          <t>Qy60zmfb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>okunuki kanji</t>
+          <t>barry boubacar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>hnqDstcS</t>
+          <t>fXkuXeTh</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>castrop jens</t>
+          <t>dejanovic daniel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>I1JWh0I4</t>
+          <t>E7iNxRIK</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>flick florian</t>
+          <t>wachs marc</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>zsLgxeCo</t>
+          <t>b7ugRnYc</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>jander caspar</t>
+          <t>cesen kristjan</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>lURc3Lpo</t>
+          <t>GWsqyZKA</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>pick florian</t>
+          <t>nazarov dimitrij</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>rHUQL532</t>
+          <t>EuUR0Lpp</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>schleimer lukas</t>
+          <t>berlinski ron</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>AJxwkipQ</t>
+          <t>dWQIRGp0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>heekeren justin</t>
+          <t>reimann dominik</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ddk0fpFO</t>
+          <t>nT3WIdHQ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>gantenbein adrian</t>
+          <t>hugonet jean</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Wfl5qKf9</t>
+          <t>EsnjdRBb</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>cisse ibrahima</t>
+          <t>mathisen marcus</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6DV32J3r</t>
+          <t>dClubWya</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>kaminski marcin</t>
+          <t>heber daniel</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>EPljTOtA</t>
+          <t>SzPX3jyU</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>murkin derry john</t>
+          <t>el hankouri mo</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>fDRz02r7</t>
+          <t>fH72vUIc</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>schallenberg ron</t>
+          <t>gnaka silas</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>nwBJRX3k</t>
+          <t>Kr4UWDeF</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>bachmann janik</t>
+          <t>omer el zein abu bekir</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>OUIcAVnP</t>
+          <t>xA8O15U4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>sylla moussa</t>
+          <t>musonda lubambo</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Cxnyxxgo</t>
+          <t>hjh8FYxE</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>karaman kenan</t>
+          <t>teixera bryan</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>rD62a0HL</t>
+          <t>UgcDv2mo</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>mohr tobias</t>
+          <t>burcu livan</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>00CSnIud</t>
+          <t>xnYgdAQ0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>hojlund emil</t>
+          <t>kaars martijn</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>CYhM4Z9N</t>
+          <t>zF8qPcIa</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>forkel dustin</t>
+          <t>becker lucas</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>YsfI5FfH</t>
+          <t>UBnS76xA</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>janisch tim</t>
+          <t>karada ouassim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>xxMuA1lC</t>
+          <t>vRpwkDf6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>karafiat ondrej</t>
+          <t>korb sascha</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fRViBeZ4</t>
+          <t>QkAyFGbj</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>lubach rafael</t>
+          <t>kovacic oliver</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>QPegJQ59</t>
+          <t>UuanyrLn</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>mathenia christian</t>
+          <t>mensah stephan</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>QszFtnum</t>
+          <t>6L1ZwbTE</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>seidel nick</t>
+          <t>mesanovic almin</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>UNcy9ySd</t>
+          <t>b5pRwkgM</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>sevcik michal</t>
+          <t>mustafa valdrin</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>xn1K9Ep6</t>
+          <t>MiNO2FrA</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>tzimas stefanos</t>
+          <t>pfeifer irwin</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>YVGPu1iB</t>
+          <t>vkahpHjE</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>aydin mehmet can</t>
+          <t>unlucifci onur</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>zyIBok7d</t>
+          <t>4dIJUitM</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>bulut taylan</t>
+          <t>amaechi xavier</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>4voxenxD</t>
+          <t>Gbn7WgOf</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>donkor anton leander</t>
+          <t>dzogovic eldin</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4YlHypVh</t>
+          <t>EkMrawol</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>gruger max</t>
+          <t>ito tatsuya</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>6DQejPXt</t>
+          <t>pEQYX0TC</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>hoffmann ron thorben</t>
+          <t>krempicki connor</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>tblOaBDU</t>
+          <t>QLxRGC6m</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>polter sebastian</t>
+          <t>kruth noah</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>vwzPuSdM</t>
+          <t>lldT3gXT</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>sanchez felipe</t>
+          <t>marusic aleksa</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>4vZGRgLG</t>
+          <t>nLuvpPGf</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>seguin paul</t>
+          <t>michel falko</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>4InA4HVE</t>
+          <t>QVb7v3D2</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>wasinski martin</t>
+          <t>muller tobias</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>l4haZLZ5</t>
+          <t>4vJQvilJ</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>valentini enrico</t>
+          <t>nollenberger alexander</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>l4haZLZ5</t>
+          <t>vkahpHjE</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>valentini enrico</t>
+          <t>unlucifci onur</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>Y1uqqiIe</t>
+          <t>vkahpHjE</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>soares danilo</t>
+          <t>unlucifci onur</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>CYhM4Z9N</t>
+          <t>GWsqyZKA</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>forkel dustin</t>
+          <t>nazarov dimitrij</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>CYhM4Z9N</t>
+          <t>b5pRwkgM</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>forkel dustin</t>
+          <t>mustafa valdrin</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>YeWnSuDP</t>
+          <t>b5pRwkgM</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>okunuki kanji</t>
+          <t>mustafa valdrin</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>xxMuA1lC</t>
+          <t>EuUR0Lpp</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>karafiat ondrej</t>
-        </is>
-      </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>xxMuA1lC</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>karafiat ondrej</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>hnqDstcS</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>castrop jens</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>YVGPu1iB</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>aydin mehmet can</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>YVGPu1iB</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>aydin mehmet can</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>00CSnIud</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>hojlund emil</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>4voxenxD</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>donkor anton leander</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
-        <is>
-          <t>4voxenxD</t>
-        </is>
-      </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>donkor anton leander</t>
-        </is>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>rD62a0HL</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>mohr tobias</t>
-        </is>
-      </c>
+          <t>berlinski ron</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="inlineStr"/>
       <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="inlineStr"/>
-      <c r="DI4" t="inlineStr"/>
-      <c r="DJ4" t="inlineStr"/>
-      <c r="DK4" t="inlineStr"/>
-      <c r="DL4" t="inlineStr"/>
-      <c r="DM4" t="inlineStr"/>
-      <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="inlineStr"/>
-      <c r="DP4" t="inlineStr"/>
-      <c r="DQ4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>EkMrawol</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>ito tatsuya</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>EkMrawol</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>ito tatsuya</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>hjh8FYxE</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>teixera bryan</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>4vJQvilJ</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>nollenberger alexander</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>4vJQvilJ</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>nollenberger alexander</t>
+        </is>
+      </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>l4haZLZ5</t>
+          <t>SzPX3jyU</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>valentini enrico</t>
+          <t>el hankouri mo</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>fRViBeZ4</t>
+          <t>QVb7v3D2</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>lubach rafael</t>
+          <t>muller tobias</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>fRViBeZ4</t>
+          <t>QVb7v3D2</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>lubach rafael</t>
+          <t>muller tobias</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>lURc3Lpo</t>
+          <t>nT3WIdHQ</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>pick florian</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="inlineStr"/>
-      <c r="EB4" t="inlineStr"/>
-      <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr"/>
+          <t>hugonet jean</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>pEQYX0TC</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>krempicki connor</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>pEQYX0TC</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>krempicki connor</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>UgcDv2mo</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>burcu livan</t>
+        </is>
+      </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>YsfI5FfH</t>
+          <t>lldT3gXT</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>janisch tim</t>
+          <t>marusic aleksa</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>YsfI5FfH</t>
+          <t>lldT3gXT</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>janisch tim</t>
+          <t>marusic aleksa</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>rHUQL532</t>
+          <t>fH72vUIc</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>schleimer lukas</t>
+          <t>gnaka silas</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pSHsOs</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>d0rCJ6XA</t>
+          <t>bytKfJV8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>krahl julian</t>
+          <t>zadach michael</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lIkG4xvp</t>
+          <t>UD7J1ahA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>zimmer jean</t>
+          <t>yaman yasin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>YyIyM2ke</t>
+          <t>vy6zKtLK</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>elvedi jan</t>
+          <t>von der bracke daniel</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0fO4CaGi</t>
+          <t>jcHV8G6S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>heuer jannis</t>
+          <t>grgic damir</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8d13nxU4</t>
+          <t>ze8xcCme</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>wekesser erik</t>
+          <t>zeghli karim</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2mMIA66I</t>
+          <t>dCPPVPk7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>kaloc filip</t>
+          <t>wingender marcel</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>EecfGnDI</t>
+          <t>pjmAw9ms</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>tomiak boris</t>
+          <t>yeboah melchisedec</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>j3uLBTA8</t>
+          <t>IiU380w6</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ritter marlon</t>
+          <t>blagojevic igor</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>WYIHibUi</t>
+          <t>6sN6n1Rb</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>tachie richmond</t>
+          <t>tuchscherer lukas</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>843k6G9D</t>
+          <t>UL3yJz92</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>hanslik daniel</t>
+          <t>leon hysenaj</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>vsimiktN</t>
+          <t>hndVMjJN</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>opoku aaron</t>
+          <t>esmel dylan</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4lDmOHX5</t>
+          <t>0MhuM4YL</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>noll nahuel</t>
+          <t>grabara kamil</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>p4gsU4KB</t>
+          <t>j5bGWFU7</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>meyerhofer marco</t>
+          <t>lacroix maxence</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>UyDYD39g</t>
+          <t>z58rzyyp</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>jung gideon</t>
+          <t>bornauw sebastiaan</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>MklWx3Ju</t>
+          <t>AZjCvCIn</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>itter gian luca</t>
+          <t>zesiger cedric</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>SpbhoTNS</t>
+          <t>AVMjVAqt</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>asta simon</t>
+          <t>baku bote</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4ftxGNHd</t>
+          <t>z522mgfh</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>muller philipp</t>
+          <t>svanberg mattias</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>63Z1rP3l</t>
+          <t>rZTSn6gr</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>green julian</t>
+          <t>gerhardt yannick</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>E1IiAd0j</t>
+          <t>hbhnybaa</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>massimo roberto</t>
+          <t>kaminski jakub</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>Kr5mFJ31</t>
+          <t>jsOwmeQB</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>hrgota branimir</t>
+          <t>wimmer patrick</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>p6v39OGe</t>
+          <t>444Jw1Mr</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>srbeny dennis</t>
+          <t>majer lovro</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>jkXw3ddG</t>
+          <t>Glknuas7</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>futkeu noel</t>
+          <t>wind jonas</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>vFfAK508</t>
+          <t>rFC1M5i3</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>abiama dickson</t>
+          <t>heine elias</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>lnwXQmIl</t>
+          <t>KbWZXoTe</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>ache ragnar</t>
+          <t>kaiser dominik</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>jozCYOMc</t>
+          <t>OzZSnD9N</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>gyamerah jan</t>
+          <t>muller marco</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>rwtqk3Wo</t>
+          <t>4U0AKqMF</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>kleinhansl florian</t>
+          <t>rosbach sebastian</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>tddjZy0T</t>
+          <t>6eMj0Fz1</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>klement phillipp</t>
+          <t>sauer tizian</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>WAGLIfPd</t>
+          <t>vNVGfble</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>mause jannik</t>
+          <t>schulte wisserman linus</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0dT23r7q</t>
+          <t>rBK5BBhi</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>raschl tobias</t>
+          <t>senguel beykan</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>YJ7XkHc6</t>
+          <t>xE5VL5HE</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>robinson leon</t>
+          <t>vdovychenko illia</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>48tkiDoS</t>
+          <t>v9Kbbg5D</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>consbruch jomaine</t>
+          <t>weber steffen</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>KdxqdGYD</t>
+          <t>zNES8u80</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>dietz maximilian</t>
+          <t>akaegbobi jonathan</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>vgFlmAm5</t>
+          <t>zgcECIjF</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>giesselmann niko</t>
+          <t>broger bennit</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>Grp8cIEl</t>
+          <t>2BI6b6Qj</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>korber nils</t>
+          <t>cozza nicolas</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>INqpznVj</t>
+          <t>21jDsx0f</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>mhamdi oualid</t>
+          <t>dardai bence</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>x6zn4GUo</t>
+          <t>Aym7cCCj</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>michalski damian</t>
+          <t>fischer kilian</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>A3uQrIzI</t>
+          <t>pIMPjP8B</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>munz reno</t>
+          <t>jenz moritz</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>GMeZlrII</t>
+          <t>OYbFR8ut</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>popp leander</t>
+          <t>muller marius</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>jLRGx0gk</t>
+          <t>vo28XMg3</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>wagner matti</t>
+          <t>neininger till</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>WAGLIfPd</t>
+          <t>WSswmxBa</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>mause jannik</t>
+          <t>tiago tomas</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>WAGLIfPd</t>
+          <t>OzZSnD9N</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>mause jannik</t>
+          <t>muller marco</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>WYIHibUi</t>
+          <t>OzZSnD9N</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>tachie richmond</t>
+          <t>muller marco</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>lnwXQmIl</t>
+          <t>pjmAw9ms</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>ache ragnar</t>
+          <t>yeboah melchisedec</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>lnwXQmIl</t>
+          <t>KbWZXoTe</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>ache ragnar</t>
+          <t>kaiser dominik</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2mMIA66I</t>
+          <t>KbWZXoTe</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>kaloc filip</t>
+          <t>kaiser dominik</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>jozCYOMc</t>
+          <t>UL3yJz92</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>gyamerah jan</t>
+          <t>leon hysenaj</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>jozCYOMc</t>
+          <t>vNVGfble</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>gyamerah jan</t>
+          <t>schulte wisserman linus</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>lIkG4xvp</t>
+          <t>vNVGfble</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>zimmer jean</t>
+          <t>schulte wisserman linus</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>vgFlmAm5</t>
+          <t>IiU380w6</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>giesselmann niko</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>vgFlmAm5</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>giesselmann niko</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>E1IiAd0j</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>massimo roberto</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>KdxqdGYD</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>dietz maximilian</t>
-        </is>
-      </c>
-      <c r="DB5" t="inlineStr">
-        <is>
-          <t>KdxqdGYD</t>
-        </is>
-      </c>
-      <c r="DC5" t="inlineStr">
-        <is>
-          <t>dietz maximilian</t>
-        </is>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>p4gsU4KB</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>meyerhofer marco</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>48tkiDoS</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>consbruch jomaine</t>
-        </is>
-      </c>
+          <t>blagojevic igor</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>48tkiDoS</t>
+          <t>Aym7cCCj</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>consbruch jomaine</t>
+          <t>fischer kilian</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>p6v39OGe</t>
+          <t>Aym7cCCj</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>srbeny dennis</t>
+          <t>fischer kilian</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>GMeZlrII</t>
+          <t>j5bGWFU7</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>popp leander</t>
+          <t>lacroix maxence</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>GMeZlrII</t>
+          <t>WSswmxBa</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>popp leander</t>
+          <t>tiago tomas</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>jkXw3ddG</t>
+          <t>WSswmxBa</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>futkeu noel</t>
+          <t>tiago tomas</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>CdGwhV3n</t>
+          <t>Glknuas7</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>spahic avdo</t>
+          <t>wind jonas</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>0dT23r7q</t>
+          <t>21jDsx0f</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>raschl tobias</t>
+          <t>dardai bence</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>0dT23r7q</t>
+          <t>21jDsx0f</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>raschl tobias</t>
+          <t>dardai bence</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>843k6G9D</t>
+          <t>z522mgfh</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>hanslik daniel</t>
+          <t>svanberg mattias</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>x6zn4GUo</t>
+          <t>zgcECIjF</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>michalski damian</t>
+          <t>broger bennit</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>x6zn4GUo</t>
+          <t>zgcECIjF</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>michalski damian</t>
+          <t>broger bennit</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>4ftxGNHd</t>
+          <t>AVMjVAqt</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>muller philipp</t>
+          <t>baku bote</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr"/>
@@ -3758,713 +3814,6 @@
       <c r="EJ5" t="inlineStr"/>
       <c r="EK5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>StuiCwhJ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>S61OwR4A</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>gebhardt felix</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CGE2sm8F</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>saller benedikt</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>pdibd5af</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ballas florian</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>fJ7n0LTa</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>breunig louis</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>jcdPxHgs</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>schonfelder oscar</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2ksQjZTe</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>proger kai</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>GIIxXLKM</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ernst sebastian</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Gt5Hjtif</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>geipl andreas</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>I7rPshxq</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>viet christian</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>jFJHrLbo</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>kother dominik</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>jNTX1fbc</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>kuhlwetter christian</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>hWgi894t</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>ortag christian</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>AeFBlVAF</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>gaal tom</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>pQtfFS0b</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>reichert johannes</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>tzVe0ks3</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>strompf philipp</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>dv6ASA22</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>allgeier bastian</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>KdIMFRBK</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>maier philipp</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>vRf1i1uQ</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>brandt max</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>CCQ1XnWk</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>roesch romario</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>Igom1Hq7</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>chessa dennis</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>QDlMCo6E</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>krattenmacher maurice</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>xhJCltvh</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>higl felix</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>EPcoFv36</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>bittroff alexander</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>658JMo90</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>bulic rasim</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>rHJa70yO</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>ganaus noah</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>n7CbWHO8</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>hein bryan</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>02rHnnnB</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>hottmann eric</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>hSia4qTi</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>ochojski nico</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>dxi8kT74</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>ouro tagba mansour</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>6qXZFscl</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>pollersbeck julian</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>jHaFpGhl</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>castelle niklas horst</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>biFABo7b</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>hyrylainen luka</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>zZzHBoll</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>keller aaron</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>h4kxWnHJ</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>kolbe niklas</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>Uk5rXoFR</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>ludwig andreas</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>xxmPNHln</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>meier jonathan</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>WYsZC6xm</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>seybold marvin</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>Eu3z7RfU</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>stoll lennart</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>AqJh2aZt</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>telalovic semir</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>rHJa70yO</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>ganaus noah</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>rHJa70yO</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>ganaus noah</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>jNTX1fbc</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>kuhlwetter christian</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>658JMo90</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>bulic rasim</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>658JMo90</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>bulic rasim</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>Gt5Hjtif</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>geipl andreas</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>vcFll0Lj</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>ziegele robin</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>vcFll0Lj</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>ziegele robin</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>jFJHrLbo</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>kother dominik</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>biFABo7b</t>
-        </is>
-      </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>hyrylainen luka</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>biFABo7b</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>hyrylainen luka</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>KdIMFRBK</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>maier philipp</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>h4kxWnHJ</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>kolbe niklas</t>
-        </is>
-      </c>
-      <c r="DB6" t="inlineStr">
-        <is>
-          <t>h4kxWnHJ</t>
-        </is>
-      </c>
-      <c r="DC6" t="inlineStr">
-        <is>
-          <t>kolbe niklas</t>
-        </is>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>AeFBlVAF</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>gaal tom</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>zZzHBoll</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>keller aaron</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>zZzHBoll</t>
-        </is>
-      </c>
-      <c r="DI6" t="inlineStr">
-        <is>
-          <t>keller aaron</t>
-        </is>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>CCQ1XnWk</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>roesch romario</t>
-        </is>
-      </c>
-      <c r="DL6" t="inlineStr">
-        <is>
-          <t>AqJh2aZt</t>
-        </is>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>telalovic semir</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>AqJh2aZt</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>telalovic semir</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>Igom1Hq7</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>chessa dennis</t>
-        </is>
-      </c>
-      <c r="DR6" t="inlineStr">
-        <is>
-          <t>vcFll0Lj</t>
-        </is>
-      </c>
-      <c r="DS6" t="inlineStr">
-        <is>
-          <t>ziegele robin</t>
-        </is>
-      </c>
-      <c r="DT6" t="inlineStr">
-        <is>
-          <t>dxi8kT74</t>
-        </is>
-      </c>
-      <c r="DU6" t="inlineStr">
-        <is>
-          <t>ouro tagba mansour</t>
-        </is>
-      </c>
-      <c r="DV6" t="inlineStr">
-        <is>
-          <t>dxi8kT74</t>
-        </is>
-      </c>
-      <c r="DW6" t="inlineStr">
-        <is>
-          <t>ouro tagba mansour</t>
-        </is>
-      </c>
-      <c r="DX6" t="inlineStr">
-        <is>
-          <t>2ksQjZTe</t>
-        </is>
-      </c>
-      <c r="DY6" t="inlineStr">
-        <is>
-          <t>proger kai</t>
-        </is>
-      </c>
-      <c r="DZ6" t="inlineStr">
-        <is>
-          <t>jHaFpGhl</t>
-        </is>
-      </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>castelle niklas horst</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
-        <is>
-          <t>jHaFpGhl</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr">
-        <is>
-          <t>castelle niklas horst</t>
-        </is>
-      </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>QDlMCo6E</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>krattenmacher maurice</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>hSia4qTi</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
-        <is>
-          <t>ochojski nico</t>
-        </is>
-      </c>
-      <c r="EH6" t="inlineStr">
-        <is>
-          <t>hSia4qTi</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>ochojski nico</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>CGE2sm8F</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>saller benedikt</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,4331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AqV0VUgU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ronnow frederik</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>W0aQEQqI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>doekhi danilho</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>U3OLd4oq</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>vogt kevin</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rmsjwZMd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>leite diogo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>IRCnlDD8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>haberer janik</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>YJUO3rKf</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tousart lucas</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>nDdRIHZI</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>khedira rani</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>KIEP1A93</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>rothe tom</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Ik1CWJ23</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>hollerbach benedict</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>K6XFTXqT</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>siebatcheu theoson</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vXXE0beb</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vertessen yorbe</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>zJ3yuRdk</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>vasilj nikola</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Cj73M6rk</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>wahl hauke</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>remhb0a6</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>smith eric</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>pjkQSCuk</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>mets karol</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>zXOjivLH</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>treu philipp</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>SvwMecZH</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>irvine jackson</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>GSyFAUT5</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>ritzka lars</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>z7Kd7nZd</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>wagner robert</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>rVehg4DU</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>guilavogui morgan</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>CCdjFJCk</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>eggestein johannes</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>UsQXxleR</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>benes laszlo</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>bmevVUsT</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>jeong woo yeong</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>rFji0QVT</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>kemlein aljoscha</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>WtK79lGh</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>querfeld leopold</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>fVThrU8C</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>roussillon jerome</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>8GBj8NFA</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>schafer andras</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>fPL4Y2AK</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>schwolow alexander</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>ObQ0AIvH</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>skarke tim</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>drCdG1r7</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>trimmel christopher</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>E7kAr9I9</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>afolayan oladapo</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>z9KGxdKj</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>albers andreas</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>bHrYrgOk</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>banks scott</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>hpqsBljc</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>boukhalfa carlo</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>xn6dTjkQ</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>dzwigala adam</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>8CoPwjx5</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>nemeth david</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>6BJTL9uJ</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>saliakas manolis</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>nNQpJoz5</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>voll ben alexander</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>8GBj8NFA</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>schafer andras</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>8GBj8NFA</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>schafer andras</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>YJUO3rKf</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>tousart lucas</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>UsQXxleR</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>benes laszlo</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>UsQXxleR</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>benes laszlo</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>vXXE0beb</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>vertessen yorbe</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>ObQ0AIvH</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>skarke tim</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>ObQ0AIvH</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>skarke tim</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Ik1CWJ23</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>hollerbach benedict</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>bmevVUsT</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>jeong woo yeong</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>bmevVUsT</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>jeong woo yeong</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>K6XFTXqT</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>siebatcheu theoson</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>WtK79lGh</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>querfeld leopold</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>WtK79lGh</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>querfeld leopold</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>KIEP1A93</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>rothe tom</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>xn6dTjkQ</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>dzwigala adam</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>xn6dTjkQ</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>dzwigala adam</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>remhb0a6</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>smith eric</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>z7Kd7nZd</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>wagner robert</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>E7kAr9I9</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>afolayan oladapo</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>E7kAr9I9</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>afolayan oladapo</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>rVehg4DU</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>guilavogui morgan</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>hpqsBljc</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>boukhalfa carlo</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>hpqsBljc</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>boukhalfa carlo</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>GSyFAUT5</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>ritzka lars</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>z9KGxdKj</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>albers andreas</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>z9KGxdKj</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>albers andreas</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>CCdjFJCk</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>eggestein johannes</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>dnpDxpQf</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>volland kevin</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>SGe0wGjI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IJQn20qM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kastenmeier florian</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OrOFQncs</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>iyoha emmanuel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>llF3GFBo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>hoffmann andre</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>nB0nG58b</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>oberdorf tim</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bNoBBKDd</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gavory nicolas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>WIZ6iQEQ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>klaus felix</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>bDD84LZO</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>zimmermann matthias</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>xtsqO2z0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>johannesson isak</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>tdzULTXb</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>kownacki dawid</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>pGbfkpdp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>zieler ron robert</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>EwiNuF2j</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>muroya sei</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>pbQe8KLk</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>neumann phil</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>jXbmuyxr</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>knight josh</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>z7yOJYMd</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>ezeh brooklyn</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>8ljKAJPh</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>lee hyun ju</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2qfaierQ</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>christiansen max</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>MHCUmJt8</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>leopold enzo</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>K8fS4hgT</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>rochelt jannik</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Wz91fbh7</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>nielsen havard</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>UmXoNi4H</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>ngankam jessic</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>zLNzuz1T</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>affo karim</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Mkhbm4fo</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>de wijs jordy</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>xOXZ2PxR</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>jastrzembski dennis</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>I7B78NeJ</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>kwasigroch robert</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>IgzqNpaO</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>mbamba noah</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>MDy44NH5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>pejcinovic dzenan</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>YV51rANA</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>quarshie joshua</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>pnf2rSQi</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>sobottka marcel</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>I5L7U2jR</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>dehm jannik</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>Eg3YK4MG</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>gindorf lars</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>hGTaHOb3</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>kunze fabian</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>zPaQxes0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>oudenne kolja</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>nuJC7uWq</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>tresoldi nicolo</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>Sz9Ehva5</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>uhlmann eric</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>AyEI4rkI</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>voglsammer andreas</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>vXHxJMUe</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>wdowik bartlomiej</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>6mRlSO05</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>weinkauf leo</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>lvfGmMDJ</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>niemiec jonah</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>WIZ6iQEQ</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>klaus felix</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>MDy44NH5</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>pejcinovic dzenan</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>MDy44NH5</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>pejcinovic dzenan</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>tdzULTXb</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>kownacki dawid</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>pnf2rSQi</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>sobottka marcel</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>pnf2rSQi</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>sobottka marcel</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>CQ7WHnQO</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>schmidt danny</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>IgzqNpaO</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>mbamba noah</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>IgzqNpaO</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>mbamba noah</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>nqadvVA9</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>rossmann tim</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>Eg3YK4MG</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>gindorf lars</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>Eg3YK4MG</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>gindorf lars</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>8ljKAJPh</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>lee hyun ju</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>nuJC7uWq</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>tresoldi nicolo</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>nuJC7uWq</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>tresoldi nicolo</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>K8fS4hgT</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>rochelt jannik</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>vXHxJMUe</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>wdowik bartlomiej</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>vXHxJMUe</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>wdowik bartlomiej</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>z7yOJYMd</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>ezeh brooklyn</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>AyEI4rkI</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>voglsammer andreas</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>AyEI4rkI</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>voglsammer andreas</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>UmXoNi4H</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>ngankam jessic</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>I5L7U2jR</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>dehm jannik</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>I5L7U2jR</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>dehm jannik</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>EwiNuF2j</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>muroya sei</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+      <c r="EX3" t="inlineStr"/>
+      <c r="EY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vs08wy8F</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S61OwR4A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>gebhardt felix</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CGE2sm8F</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>saller benedikt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pdibd5af</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ballas florian</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>fJ7n0LTa</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>breunig louis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>jcdPxHgs</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>schonfelder oscar</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GIIxXLKM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ernst sebastian</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Gt5Hjtif</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>geipl andreas</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2ksQjZTe</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>proger kai</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>I7rPshxq</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>viet christian</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>jFJHrLbo</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>kother dominik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>jNTX1fbc</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>kuhlwetter christian</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4lDmOHX5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>noll nahuel</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>p4gsU4KB</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>meyerhofer marco</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>UyDYD39g</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>jung gideon</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>MklWx3Ju</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>itter gian luca</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>SpbhoTNS</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>asta simon</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>KdxqdGYD</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>dietz maximilian</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>63Z1rP3l</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>green julian</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>E1IiAd0j</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>massimo roberto</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Kr5mFJ31</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>hrgota branimir</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>jkXw3ddG</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>futkeu noel</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>p6v39OGe</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>srbeny dennis</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>2794IiQ0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>bauer jonas</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>EPcoFv36</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>bittroff alexander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>n7CbWHO8</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>hein bryan</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>hSia4qTi</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>ochojski nico</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>6qXZFscl</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>pollersbeck julian</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>vcFll0Lj</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>ziegele robin</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>hUHPtQt7</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>banse sacha</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Grp8cIEl</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>korber nils</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>INqpznVj</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>mhamdi oualid</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>4ftxGNHd</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>muller philipp</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>rHQfYOz6</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>mustapha suliman</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>GMeZlrII</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>popp leander</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>rHJa70yO</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>ganaus noah</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>GIIxXLKM</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>ernst sebastian</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>658JMo90</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>bulic rasim</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>I7rPshxq</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>viet christian</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>hSia4qTi</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>ochojski nico</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>hSia4qTi</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>ochojski nico</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>CGE2sm8F</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>saller benedikt</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>02rHnnnB</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>hottmann eric</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>jNTX1fbc</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>kuhlwetter christian</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>2794IiQ0</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>bauer jonas</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>2794IiQ0</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>bauer jonas</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2ksQjZTe</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>proger kai</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>hUHPtQt7</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>banse sacha</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>hUHPtQt7</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>banse sacha</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>UyDYD39g</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>jung gideon</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>rHQfYOz6</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>mustapha suliman</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>rHQfYOz6</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>mustapha suliman</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>p6v39OGe</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>srbeny dennis</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>vgFlmAm5</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>giesselmann niko</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>SpbhoTNS</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>asta simon</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>A3uQrIzI</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>munz reno</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>E1IiAd0j</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>massimo roberto</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>48tkiDoS</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>consbruch jomaine</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>Kr5mFJ31</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>hrgota branimir</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+      <c r="EX4" t="inlineStr"/>
+      <c r="EY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>6u6i5pie</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KvpRs0se</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dedidis alexios</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>K4vSNbp8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>butzen nils</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>xMHywEPo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>el haija khalid</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pGBzvY5j</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>reddemann soren kurt</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>thNwIkl6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>kramer paul</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6o8fXpDt</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>schau justin</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>C0p6OSP4</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>gipson ken</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>6gJyXBrf</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>muqaj hamza</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0fU9OS9f</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>richter joel</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>YaHpiUBr</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>weinhauer erik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>bZshci1p</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>sezer cemal</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>tIXuiy4C</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>kovar matej</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dxkz9WG0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>arthur</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>d4z5zQ7g</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>tapsoba edmond</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2yf8EcuE</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>tah jonathan</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>zog0NOeM</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>belocian jeanuel</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>QD7noPXB</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>garcia aleix</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>zDjAwp82</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>andrich robert</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>QRtPmK69</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>tella nathan</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>xvCz3Gwd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>hofmann jonas</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>82ETy0Me</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>adli amine</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>WzQQSSfc</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>schick patrik</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>ni9fEtMF</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>hessel maxim</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>MiQRvA3I</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>kampe paul</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>dKivR1Hu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>liesegang marius</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>xAuZ1slR</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>prokopenko alexander</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>SjjlN2Gj</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>seidemann kay</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>WC2tydGd</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>werner jannes</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>xvqdoWXA</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>zank benjamin</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>SjJ6pCvC</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>frimpong jeremie</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>6cAIrW5Q</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>grimaldo alex</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>2TTElOLP</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>hincapie pedro</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>fB4FKbSB</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>lomb niklas</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>nHOw5Jjn</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>onyeka francis</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>Wl6Cl3q8</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>raterink othniel</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>ldk7Wmoe</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>stepanov artem</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>0Q5gjImi</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>wirtz florian</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>QBHCDKff</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>xhaka granit</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>SjjlN2Gj</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>seidemann kay</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>SjjlN2Gj</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>seidemann kay</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0fU9OS9f</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>richter joel</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>xvqdoWXA</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>zank benjamin</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>xvqdoWXA</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>zank benjamin</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>bZshci1p</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>sezer cemal</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>xAuZ1slR</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>prokopenko alexander</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>xAuZ1slR</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>prokopenko alexander</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>C0p6OSP4</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>gipson ken</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>6cAIrW5Q</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>grimaldo alex</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>6cAIrW5Q</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>grimaldo alex</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>dxkz9WG0</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>arthur</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>0Q5gjImi</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>wirtz florian</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>0Q5gjImi</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>wirtz florian</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>82ETy0Me</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>adli amine</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>SjJ6pCvC</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>frimpong jeremie</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>SjJ6pCvC</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>frimpong jeremie</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>QRtPmK69</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>tella nathan</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>QBHCDKff</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>xhaka granit</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>QBHCDKff</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>xhaka granit</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>zDjAwp82</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>andrich robert</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+      <c r="EX5" t="inlineStr"/>
+      <c r="EY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dEikH1Kb</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>behrens morten</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GfxLwyRf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>schad dominik</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COALarg5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>frenkert lukas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>W629DD2p</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>peatow torge</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2VV3mWal</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>kirkeskov mikkel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>joxYnHwl</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>bazzoli luca</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>tMs28wMD</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>hendrix jorrit</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>febm46cJ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>lorenz marc</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>vqACZfUA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>nemeth andras</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0jQoFve6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>grodowski joel</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Igk6vzlT</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>nubel alexander</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>I9avdeat</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>stenzel pascal</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>QRcni8Si</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>chase anrie</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>f1kf4eiH</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>chabot julian</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>x0JgoYBA</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>mittelstadt maximilian</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>GQOPPSgM</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>rieder fabian</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>zc2VFBzR</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>karazor atakan</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0hF2GIXS</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>stiller angelo</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>bczcNJFB</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>fuhrich chris</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>4YDUd1at</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>woltemade nick</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>dIsZ5Eyb</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>demirovic ermedin</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>b5ojgUKT</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>bolay luca</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>hAYcztZo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>deters thorben</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>GdTT8aB4</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>mees joshua</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>xbHTqKPs</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>schenk johannes</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0AIlcS72</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>scherder simon</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>pC5Aa7Fa</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>ter horst jano</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>MTjX2S5c</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>bredlow fabian</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>x2tZQYZD</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>hendriks ramon</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>bXYV35NK</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>keitel yannik</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>hYP3hnMa</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>kratzig frans</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>UTtpcjym</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>leweling jamie</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>tnaRyr62</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>millot enzo</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>SIml2Qes</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>silas</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>tUHAdtMH</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>undav deniz</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>febm46cJ</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>lorenz marc</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>joxYnHwl</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>bazzoli luca</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>GdTT8aB4</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>mees joshua</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>GdTT8aB4</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>mees joshua</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>tMs28wMD</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>hendrix jorrit</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>vqACZfUA</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>nemeth andras</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>b5ojgUKT</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>bolay luca</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>b5ojgUKT</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>bolay luca</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>0jQoFve6</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>grodowski joel</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>hYP3hnMa</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>kratzig frans</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>hYP3hnMa</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>kratzig frans</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>x0JgoYBA</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>mittelstadt maximilian</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>tUHAdtMH</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>undav deniz</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>tUHAdtMH</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>undav deniz</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>dIsZ5Eyb</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>demirovic ermedin</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>UTtpcjym</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>leweling jamie</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>UTtpcjym</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>leweling jamie</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>bczcNJFB</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>fuhrich chris</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>x2tZQYZD</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>hendriks ramon</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>x2tZQYZD</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>hendriks ramon</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>I9avdeat</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>stenzel pascal</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>GQOPPSgM</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>rieder fabian</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr"/>
+      <c r="EO6" t="inlineStr"/>
+      <c r="EP6" t="inlineStr"/>
+      <c r="EQ6" t="inlineStr"/>
+      <c r="ER6" t="inlineStr"/>
+      <c r="ES6" t="inlineStr"/>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+      <c r="EX6" t="inlineStr"/>
+      <c r="EY6" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EY6"/>
+  <dimension ref="A1:FK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,4023 +731,8080 @@
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_home_9</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_home_9</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_1</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_1</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_2</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_2</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_3</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_3</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_4</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_4</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_5</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_5</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_6</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_6</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_7</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_7</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_8</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_8</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_away_9</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_away_9</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_1</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_2</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_3</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_4</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_5</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_6</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_13</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_13</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_14</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_14</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_15</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_15</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_1</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_2</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_3</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_4</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_5</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_6</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_7</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_8</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_9</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_10</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_11</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_12</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AqV0VUgU</t>
+          <t>tIXuiy4C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ronnow frederik</t>
+          <t>kovar matej</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>W0aQEQqI</t>
+          <t>d4z5zQ7g</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>doekhi danilho</t>
+          <t>tapsoba edmond</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>U3OLd4oq</t>
+          <t>2yf8EcuE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>vogt kevin</t>
+          <t>tah jonathan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>rmsjwZMd</t>
+          <t>2TTElOLP</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>leite diogo</t>
+          <t>hincapie pedro</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IRCnlDD8</t>
+          <t>SjJ6pCvC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>haberer janik</t>
+          <t>frimpong jeremie</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>YJUO3rKf</t>
+          <t>QBHCDKff</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>tousart lucas</t>
+          <t>xhaka granit</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nDdRIHZI</t>
+          <t>QD7noPXB</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>khedira rani</t>
+          <t>garcia aleix</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>KIEP1A93</t>
+          <t>6cAIrW5Q</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>rothe tom</t>
+          <t>grimaldo alex</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Ik1CWJ23</t>
+          <t>xlu6948L</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>hollerbach benedict</t>
+          <t>terrier martin</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>K6XFTXqT</t>
+          <t>0Q5gjImi</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>siebatcheu theoson</t>
+          <t>wirtz florian</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>vXXE0beb</t>
+          <t>dd4GDL19</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>vertessen yorbe</t>
+          <t>boniface victor</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>zJ3yuRdk</t>
+          <t>lYMcgOCg</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>vasilj nikola</t>
+          <t>gulacsi peter</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Cj73M6rk</t>
+          <t>KI3jSJTG</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>wahl hauke</t>
+          <t>klostermann lukas</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>remhb0a6</t>
+          <t>6X0C61vo</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>smith eric</t>
+          <t>lukeba castello</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>pjkQSCuk</t>
+          <t>6DL0LD7a</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>mets karol</t>
+          <t>bitshiabu el chadaille</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>zXOjivLH</t>
+          <t>xEK5LMdo</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>treu philipp</t>
+          <t>henrichs benjamin</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>SvwMecZH</t>
+          <t>lYg9oNUk</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>irvine jackson</t>
+          <t>haidara amadou</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>GSyFAUT5</t>
+          <t>ttXwlOTi</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>ritzka lars</t>
+          <t>kampl kevin</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>z7Kd7nZd</t>
+          <t>2XVqEh8k</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>wagner robert</t>
+          <t>raum david</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>zqXaHPUa</t>
+          <t>noo0L9zk</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>metcalfe connor</t>
+          <t>simons xavi</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>rVehg4DU</t>
+          <t>IN2MK7Jo</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>guilavogui morgan</t>
+          <t>openda lois</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>CCdjFJCk</t>
+          <t>QDozP4IN</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>eggestein johannes</t>
+          <t>sesko benjamin</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>UsQXxleR</t>
+          <t>82ETy0Me</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>benes laszlo</t>
+          <t>adli amine</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>bmevVUsT</t>
+          <t>zDjAwp82</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>jeong woo yeong</t>
+          <t>andrich robert</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>rFji0QVT</t>
+          <t>dxkz9WG0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>kemlein aljoscha</t>
+          <t>arthur</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>WtK79lGh</t>
+          <t>zog0NOeM</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>querfeld leopold</t>
+          <t>belocian jeanuel</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>fVThrU8C</t>
+          <t>fB4FKbSB</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>roussillon jerome</t>
+          <t>lomb niklas</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8GBj8NFA</t>
+          <t>MoObMvb7</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>schafer andras</t>
+          <t>mukiele nordi</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>fPL4Y2AK</t>
+          <t>WzQQSSfc</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>schwolow alexander</t>
+          <t>schick patrik</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>ObQ0AIvH</t>
+          <t>QRtPmK69</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>skarke tim</t>
+          <t>tella nathan</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>drCdG1r7</t>
+          <t>UZRsjD5h</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>trimmel christopher</t>
+          <t>silva andre</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>E7kAr9I9</t>
+          <t>rqcu4a9O</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>afolayan oladapo</t>
+          <t>baumgartner christoph</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>z9KGxdKj</t>
+          <t>vDVD8EAA</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>albers andreas</t>
+          <t>elmas elif</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>bHrYrgOk</t>
+          <t>Mcu6Wt0C</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>banks scott</t>
+          <t>gebel viggo</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>hpqsBljc</t>
+          <t>rHwRvHQp</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>boukhalfa carlo</t>
+          <t>nusa antonio</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>xn6dTjkQ</t>
+          <t>SrWbvhrI</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>dzwigala adam</t>
+          <t>poulsen yussuf</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>8CoPwjx5</t>
+          <t>fivkoAh0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>nemeth david</t>
+          <t>seiwald nicolas</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>rcSN3FVD</t>
+          <t>AFY9ARa5</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>saad elias</t>
+          <t>vandevoordt maarten</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6BJTL9uJ</t>
+          <t>tzhSwObR</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>saliakas manolis</t>
+          <t>vermeeren arthur</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>nNQpJoz5</t>
+          <t>82ETy0Me</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>voll ben alexander</t>
+          <t>adli amine</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>8GBj8NFA</t>
+          <t>82ETy0Me</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>schafer andras</t>
+          <t>adli amine</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>8GBj8NFA</t>
+          <t>xlu6948L</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>schafer andras</t>
+          <t>terrier martin</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>YJUO3rKf</t>
+          <t>WzQQSSfc</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>tousart lucas</t>
+          <t>schick patrik</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>UsQXxleR</t>
+          <t>WzQQSSfc</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>benes laszlo</t>
+          <t>schick patrik</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>UsQXxleR</t>
+          <t>dd4GDL19</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>benes laszlo</t>
+          <t>boniface victor</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>vXXE0beb</t>
+          <t>QRtPmK69</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>vertessen yorbe</t>
+          <t>tella nathan</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>ObQ0AIvH</t>
+          <t>QRtPmK69</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>skarke tim</t>
+          <t>tella nathan</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>ObQ0AIvH</t>
+          <t>SjJ6pCvC</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>skarke tim</t>
+          <t>frimpong jeremie</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>Ik1CWJ23</t>
+          <t>dxkz9WG0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>hollerbach benedict</t>
+          <t>arthur</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>bmevVUsT</t>
+          <t>dxkz9WG0</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>jeong woo yeong</t>
+          <t>arthur</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>bmevVUsT</t>
+          <t>d4z5zQ7g</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>jeong woo yeong</t>
+          <t>tapsoba edmond</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>K6XFTXqT</t>
+          <t>fivkoAh0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>siebatcheu theoson</t>
+          <t>seiwald nicolas</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>WtK79lGh</t>
+          <t>fivkoAh0</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>querfeld leopold</t>
+          <t>seiwald nicolas</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>WtK79lGh</t>
+          <t>lYg9oNUk</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>querfeld leopold</t>
+          <t>haidara amadou</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>KIEP1A93</t>
+          <t>rHwRvHQp</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>rothe tom</t>
+          <t>nusa antonio</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>xn6dTjkQ</t>
+          <t>rHwRvHQp</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>dzwigala adam</t>
+          <t>nusa antonio</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>xn6dTjkQ</t>
+          <t>QDozP4IN</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>dzwigala adam</t>
+          <t>sesko benjamin</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>remhb0a6</t>
+          <t>rqcu4a9O</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>smith eric</t>
+          <t>baumgartner christoph</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>rcSN3FVD</t>
+          <t>rqcu4a9O</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>saad elias</t>
+          <t>baumgartner christoph</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>rcSN3FVD</t>
+          <t>ttXwlOTi</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>saad elias</t>
+          <t>kampl kevin</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>z7Kd7nZd</t>
+          <t>SrWbvhrI</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>wagner robert</t>
+          <t>poulsen yussuf</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>E7kAr9I9</t>
+          <t>SrWbvhrI</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>afolayan oladapo</t>
+          <t>poulsen yussuf</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>E7kAr9I9</t>
+          <t>IN2MK7Jo</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>afolayan oladapo</t>
+          <t>openda lois</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>rVehg4DU</t>
+          <t>tzhSwObR</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>guilavogui morgan</t>
+          <t>vermeeren arthur</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>hpqsBljc</t>
+          <t>tzhSwObR</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>boukhalfa carlo</t>
+          <t>vermeeren arthur</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>hpqsBljc</t>
+          <t>xEK5LMdo</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>boukhalfa carlo</t>
+          <t>henrichs benjamin</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>GSyFAUT5</t>
+          <t>nRZtaBXj</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>ritzka lars</t>
+          <t>hradecky lukas</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>z9KGxdKj</t>
+          <t>xEflXBhr</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>albers andreas</t>
+          <t>palacios exequiel</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>z9KGxdKj</t>
+          <t>WQdSnUfq</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>albers andreas</t>
+          <t>orban willi</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>CCdjFJCk</t>
+          <t>bs71GRSt</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>eggestein johannes</t>
+          <t>ouedraogo assan</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>WznPyl4k</t>
+          <t>M1bcCLIU</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>juranovic josip</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>WdkYVaj9</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>prtajin ivan</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>Oh6gIVja</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>stein yannic</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>dnpDxpQf</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>volland kevin</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>6y5I2kuT</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>ahlers soren</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>QwxAZ5yD</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>burchert sascha</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>rD3WL6oI</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>zoller simon</t>
-        </is>
-      </c>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="inlineStr"/>
+      <c r="EX2" t="inlineStr"/>
+      <c r="EY2" t="inlineStr"/>
+      <c r="EZ2" t="inlineStr"/>
+      <c r="FA2" t="inlineStr"/>
+      <c r="FB2" t="inlineStr"/>
+      <c r="FC2" t="inlineStr"/>
+      <c r="FD2" t="inlineStr"/>
+      <c r="FE2" t="inlineStr"/>
+      <c r="FF2" t="inlineStr"/>
+      <c r="FG2" t="inlineStr"/>
+      <c r="FH2" t="inlineStr"/>
+      <c r="FI2" t="inlineStr"/>
+      <c r="FJ2" t="inlineStr"/>
+      <c r="FK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SGe0wGjI</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IJQn20qM</t>
+          <t>Igox818S</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kastenmeier florian</t>
+          <t>drewes patrick</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OrOFQncs</t>
+          <t>rHIRgwGG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>iyoha emmanuel</t>
+          <t>passlack felix</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>llF3GFBo</t>
+          <t>EcnpcDEj</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>hoffmann andre</t>
+          <t>medic jakov</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>nB0nG58b</t>
+          <t>SM5LWds5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>oberdorf tim</t>
+          <t>masovic erhan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bNoBBKDd</t>
+          <t>E9AoPVT6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>gavory nicolas</t>
+          <t>wittek maximilian</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>WIZ6iQEQ</t>
+          <t>xCntHJ58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>klaus felix</t>
+          <t>losilla anthony</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>bDD84LZO</t>
+          <t>Egd7aMH9</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zimmermann matthias</t>
+          <t>de wit dani</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>xtsqO2z0</t>
+          <t>Mi7Mao9U</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>johannesson isak</t>
+          <t>sissoko ibrahima</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>nqadvVA9</t>
+          <t>lWQqSFyt</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>rossmann tim</t>
+          <t>bero matus</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CQ7WHnQO</t>
+          <t>2JfL568j</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>schmidt danny</t>
+          <t>hofmann philipp</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>tdzULTXb</t>
+          <t>p22YQwxH</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>kownacki dawid</t>
+          <t>broschinski moritz</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>pGbfkpdp</t>
+          <t>IwP3NZs5</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>zieler ron robert</t>
+          <t>omlin jonas</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>EwiNuF2j</t>
+          <t>GpuBpqKP</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>muroya sei</t>
+          <t>scally joe</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>pbQe8KLk</t>
+          <t>xGFA759a</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>neumann phil</t>
+          <t>itakura ko</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>jXbmuyxr</t>
+          <t>fZO9OHIM</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>knight josh</t>
+          <t>elvedi nico</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>z7yOJYMd</t>
+          <t>YZUjjz4A</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>ezeh brooklyn</t>
+          <t>netz luca</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8ljKAJPh</t>
+          <t>xhaCyR2q</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>lee hyun ju</t>
+          <t>sander philipp</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2qfaierQ</t>
+          <t>2wwMMwAa</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>christiansen max</t>
+          <t>weigl julian</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>MHCUmJt8</t>
+          <t>pWiv7csf</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>leopold enzo</t>
+          <t>honorat franck</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>K8fS4hgT</t>
+          <t>6XndQuug</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>rochelt jannik</t>
+          <t>stoger kevin</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Wz91fbh7</t>
+          <t>0rfLpu2t</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>nielsen havard</t>
+          <t>plea alassane</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>UmXoNi4H</t>
+          <t>4EFLl8xt</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>ngankam jessic</t>
+          <t>kleindienst tim</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>zLNzuz1T</t>
+          <t>U7wepPkr</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>affo karim</t>
+          <t>balde aliou</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>Mkhbm4fo</t>
+          <t>j11d0s1G</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>de wijs jordy</t>
+          <t>bamba samuel</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>xOXZ2PxR</t>
+          <t>GE24QNxi</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>jastrzembski dennis</t>
+          <t>boadu myron</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>I7B78NeJ</t>
+          <t>0xFrtR5h</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>kwasigroch robert</t>
+          <t>daschner lukas</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>IgzqNpaO</t>
+          <t>drpM6sGl</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>mbamba noah</t>
+          <t>gamboa cristian</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>lvfGmMDJ</t>
+          <t>SIMkMwB8</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>niemiec jonah</t>
+          <t>horn timo</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>MDy44NH5</t>
+          <t>E567xTf3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>pejcinovic dzenan</t>
+          <t>loosli noah</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>YV51rANA</t>
+          <t>0QZFzPEM</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>quarshie joshua</t>
+          <t>oermann tim</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>pnf2rSQi</t>
+          <t>G8pNcC0K</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>sobottka marcel</t>
+          <t>chiarodia fabio cristian</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>I5L7U2jR</t>
+          <t>zgMpZZSc</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>dehm jannik</t>
+          <t>cvancara tomas</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>Eg3YK4MG</t>
+          <t>Oj600SOn</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>gindorf lars</t>
+          <t>friedrich marvin</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>hGTaHOb3</t>
+          <t>zZ9n9OAn</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>kunze fabian</t>
+          <t>hack robin</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>zPaQxes0</t>
+          <t>lCbT3rUK</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>oudenne kolja</t>
+          <t>lainer stefan</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>nuJC7uWq</t>
+          <t>ALwvJeYD</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>tresoldi nicolo</t>
+          <t>neuhaus florian</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>Sz9Ehva5</t>
+          <t>bDOAkNvH</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>uhlmann eric</t>
+          <t>ngoumou nathan</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>AyEI4rkI</t>
+          <t>QHmvN1QT</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>voglsammer andreas</t>
+          <t>nicolas moritz</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>vXHxJMUe</t>
+          <t>jsIjP0Al</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>wdowik bartlomiej</t>
+          <t>reitz rocco</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>6mRlSO05</t>
+          <t>U7wepPkr</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>weinkauf leo</t>
+          <t>balde aliou</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>lvfGmMDJ</t>
+          <t>U7wepPkr</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>niemiec jonah</t>
+          <t>balde aliou</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>lvfGmMDJ</t>
+          <t>p22YQwxH</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>niemiec jonah</t>
+          <t>broschinski moritz</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>WIZ6iQEQ</t>
+          <t>GE24QNxi</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>klaus felix</t>
+          <t>boadu myron</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>MDy44NH5</t>
+          <t>GE24QNxi</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>pejcinovic dzenan</t>
+          <t>boadu myron</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>MDy44NH5</t>
+          <t>xCntHJ58</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>pejcinovic dzenan</t>
+          <t>losilla anthony</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>tdzULTXb</t>
+          <t>0xFrtR5h</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>kownacki dawid</t>
+          <t>daschner lukas</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>pnf2rSQi</t>
+          <t>0xFrtR5h</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>sobottka marcel</t>
+          <t>daschner lukas</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>pnf2rSQi</t>
+          <t>2JfL568j</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>sobottka marcel</t>
+          <t>hofmann philipp</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>CQ7WHnQO</t>
+          <t>G65tUuC3</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>schmidt danny</t>
+          <t>pannewig mats</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>IgzqNpaO</t>
+          <t>G65tUuC3</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>mbamba noah</t>
+          <t>pannewig mats</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>IgzqNpaO</t>
+          <t>Mi7Mao9U</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>mbamba noah</t>
+          <t>sissoko ibrahima</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>nqadvVA9</t>
+          <t>jsIjP0Al</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>rossmann tim</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
+          <t>reitz rocco</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>jsIjP0Al</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>reitz rocco</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>0rfLpu2t</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>plea alassane</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>zZ9n9OAn</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>hack robin</t>
+        </is>
+      </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>Eg3YK4MG</t>
+          <t>zZ9n9OAn</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>gindorf lars</t>
+          <t>hack robin</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>Eg3YK4MG</t>
+          <t>xhaCyR2q</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>gindorf lars</t>
+          <t>sander philipp</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>8ljKAJPh</t>
+          <t>bDOAkNvH</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>lee hyun ju</t>
+          <t>ngoumou nathan</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>nuJC7uWq</t>
+          <t>bDOAkNvH</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>tresoldi nicolo</t>
+          <t>ngoumou nathan</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>nuJC7uWq</t>
+          <t>pWiv7csf</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>tresoldi nicolo</t>
+          <t>honorat franck</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>K8fS4hgT</t>
+          <t>zgMpZZSc</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>rochelt jannik</t>
+          <t>cvancara tomas</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>vXHxJMUe</t>
+          <t>zgMpZZSc</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>wdowik bartlomiej</t>
+          <t>cvancara tomas</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>vXHxJMUe</t>
+          <t>4EFLl8xt</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>wdowik bartlomiej</t>
+          <t>kleindienst tim</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>z7yOJYMd</t>
+          <t>lCbT3rUK</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>ezeh brooklyn</t>
+          <t>lainer stefan</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>AyEI4rkI</t>
+          <t>lCbT3rUK</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>voglsammer andreas</t>
+          <t>lainer stefan</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>AyEI4rkI</t>
+          <t>YZUjjz4A</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>voglsammer andreas</t>
+          <t>netz luca</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>UmXoNi4H</t>
+          <t>MwxzFrgA</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>ngankam jessic</t>
+          <t>bernardo</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>I5L7U2jR</t>
+          <t>vcq6DJJN</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>dehm jannik</t>
+          <t>kwarteng moritz</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>I5L7U2jR</t>
+          <t>ltDOVSGt</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>dehm jannik</t>
+          <t>borges sanches yvandro</t>
         </is>
       </c>
       <c r="EJ3" t="inlineStr">
         <is>
-          <t>EwiNuF2j</t>
+          <t>MyyplBl4</t>
         </is>
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>muroya sei</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="inlineStr"/>
-      <c r="EQ3" t="inlineStr"/>
-      <c r="ER3" t="inlineStr"/>
-      <c r="ES3" t="inlineStr"/>
-      <c r="ET3" t="inlineStr"/>
-      <c r="EU3" t="inlineStr"/>
-      <c r="EV3" t="inlineStr"/>
-      <c r="EW3" t="inlineStr"/>
-      <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="inlineStr"/>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>G65tUuC3</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>pannewig mats</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>0QZFzPEM</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>oermann tim</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>0QZFzPEM</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>oermann tim</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>EcnpcDEj</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>medic jakov</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>40wafXg4</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>ordets ivan</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>dGcprQ0r</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>riemann manuel</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr"/>
+      <c r="FC3" t="inlineStr"/>
+      <c r="FD3" t="inlineStr"/>
+      <c r="FE3" t="inlineStr"/>
+      <c r="FF3" t="inlineStr"/>
+      <c r="FG3" t="inlineStr"/>
+      <c r="FH3" t="inlineStr"/>
+      <c r="FI3" t="inlineStr"/>
+      <c r="FJ3" t="inlineStr"/>
+      <c r="FK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vs08wy8F</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S61OwR4A</t>
+          <t>QqugudYS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gebhardt felix</t>
+          <t>trapp kevin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CGE2sm8F</t>
+          <t>z9f8RgUQ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>saller benedikt</t>
+          <t>tuta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pdibd5af</t>
+          <t>WzSF4nFU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ballas florian</t>
+          <t>koch robin</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>fJ7n0LTa</t>
+          <t>2NA43UrT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>breunig louis</t>
+          <t>theate arthur</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>jcdPxHgs</t>
+          <t>Ii8pjsY2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>schonfelder oscar</t>
+          <t>kristensen rasmus</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GIIxXLKM</t>
+          <t>UawLDteR</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ernst sebastian</t>
+          <t>skhiri ellyes</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Gt5Hjtif</t>
+          <t>K89S36S5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>geipl andreas</t>
+          <t>larsson hugo</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2ksQjZTe</t>
+          <t>t21cpbh2</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>proger kai</t>
+          <t>nkounkou niels</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>I7rPshxq</t>
+          <t>veaF8P5m</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>viet christian</t>
+          <t>gotze mario</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>jFJHrLbo</t>
+          <t>ltVXPlJU</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>kother dominik</t>
+          <t>ekitike hugo</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>jNTX1fbc</t>
+          <t>44pYRYIC</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>kuhlwetter christian</t>
+          <t>marmoush omar</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4lDmOHX5</t>
+          <t>MZ6BATVO</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>noll nahuel</t>
+          <t>baumann oliver</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>p4gsU4KB</t>
+          <t>CjdwXbER</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>meyerhofer marco</t>
+          <t>drexler tim</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>UyDYD39g</t>
+          <t>h8i6ur8L</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>jung gideon</t>
+          <t>stach anton</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>MklWx3Ju</t>
+          <t>OU6TrrMb</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>itter gian luca</t>
+          <t>akpoguma kevin</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>SpbhoTNS</t>
+          <t>MwBrqRha</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>asta simon</t>
+          <t>kaderabek pavel</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>KdxqdGYD</t>
+          <t>GOTDkA9I</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>dietz maximilian</t>
+          <t>promel grischa</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>63Z1rP3l</t>
+          <t>GtZAyRi8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>green julian</t>
+          <t>geiger dennis</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>E1IiAd0j</t>
+          <t>0pNTmC8s</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>massimo roberto</t>
+          <t>prass alexander</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Kr5mFJ31</t>
+          <t>6V0rWuu1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>hrgota branimir</t>
+          <t>kramaric andrej</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>jkXw3ddG</t>
+          <t>2FUsDXpd</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>futkeu noel</t>
+          <t>hlozek adam</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>p6v39OGe</t>
+          <t>QHFJHvmo</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>srbeny dennis</t>
+          <t>bulter marius</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>2794IiQ0</t>
+          <t>xtDO40Js</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>bauer jonas</t>
+          <t>amenda aurele</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>EPcoFv36</t>
+          <t>tvEgJSar</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>bittroff alexander</t>
+          <t>bahoya jean</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>658JMo90</t>
+          <t>IusyCIkS</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>bulic rasim</t>
+          <t>fares chaibi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>rHJa70yO</t>
+          <t>KdoHDRzE</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>ganaus noah</t>
+          <t>chandler timothy</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>n7CbWHO8</t>
+          <t>0xxsmCo1</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>hein bryan</t>
+          <t>collins nnamdi</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>02rHnnnB</t>
+          <t>W4tC13d7</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>hottmann eric</t>
+          <t>kaua santos</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>hSia4qTi</t>
+          <t>2ebHJb1N</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>ochojski nico</t>
+          <t>knauff ansgar</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>6qXZFscl</t>
+          <t>j5PxPTVi</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>pollersbeck julian</t>
+          <t>matanovic igor</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>vcFll0Lj</t>
+          <t>KWrYlSTD</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>ziegele robin</t>
+          <t>berisha mergim</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>hUHPtQt7</t>
+          <t>GdwP5bwG</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>banse sacha</t>
+          <t>bruun larsen jacob</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>48tkiDoS</t>
+          <t>lxAucZ4d</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>consbruch jomaine</t>
+          <t>gendrey valentin</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>vgFlmAm5</t>
+          <t>z3DBHDy0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>giesselmann niko</t>
+          <t>hranac robin</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>Grp8cIEl</t>
+          <t>Sr8rsi6C</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>korber nils</t>
+          <t>micheler florian</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>INqpznVj</t>
+          <t>QaQIZA1a</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>mhamdi oualid</t>
+          <t>nsoki stanley</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>4ftxGNHd</t>
+          <t>6LCkrtZB</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>muller philipp</t>
+          <t>philipp luca</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>A3uQrIzI</t>
+          <t>zRqIWAdG</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>munz reno</t>
+          <t>samassekou diadie</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>rHQfYOz6</t>
+          <t>Asecu8a3</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>mustapha suliman</t>
+          <t>tabakovic haris</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>GMeZlrII</t>
+          <t>j5PxPTVi</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>popp leander</t>
+          <t>matanovic igor</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>rHJa70yO</t>
+          <t>j5PxPTVi</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>ganaus noah</t>
+          <t>matanovic igor</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>rHJa70yO</t>
+          <t>ltVXPlJU</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>ganaus noah</t>
+          <t>ekitike hugo</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>GIIxXLKM</t>
+          <t>hljGyhNr</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>ernst sebastian</t>
+          <t>uzun can yilmaz</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>658JMo90</t>
+          <t>hljGyhNr</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>bulic rasim</t>
+          <t>uzun can yilmaz</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>658JMo90</t>
+          <t>veaF8P5m</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>bulic rasim</t>
+          <t>gotze mario</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>I7rPshxq</t>
+          <t>IusyCIkS</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>viet christian</t>
+          <t>fares chaibi</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>hSia4qTi</t>
+          <t>IusyCIkS</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>ochojski nico</t>
+          <t>fares chaibi</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>hSia4qTi</t>
+          <t>44pYRYIC</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>ochojski nico</t>
+          <t>marmoush omar</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>CGE2sm8F</t>
+          <t>2ebHJb1N</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>saller benedikt</t>
+          <t>knauff ansgar</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>02rHnnnB</t>
+          <t>2ebHJb1N</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>hottmann eric</t>
+          <t>knauff ansgar</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>02rHnnnB</t>
+          <t>t21cpbh2</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>hottmann eric</t>
+          <t>nkounkou niels</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>jNTX1fbc</t>
+          <t>z3DBHDy0</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>kuhlwetter christian</t>
+          <t>hranac robin</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>2794IiQ0</t>
+          <t>z3DBHDy0</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>bauer jonas</t>
+          <t>hranac robin</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>2794IiQ0</t>
+          <t>CjdwXbER</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>bauer jonas</t>
+          <t>drexler tim</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
         <is>
-          <t>2ksQjZTe</t>
+          <t>KWrYlSTD</t>
         </is>
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>proger kai</t>
+          <t>berisha mergim</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>hUHPtQt7</t>
+          <t>KWrYlSTD</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>banse sacha</t>
+          <t>berisha mergim</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>hUHPtQt7</t>
+          <t>QHFJHvmo</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>banse sacha</t>
+          <t>bulter marius</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>UyDYD39g</t>
+          <t>Sr8rsi6C</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>jung gideon</t>
+          <t>micheler florian</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>rHQfYOz6</t>
+          <t>Sr8rsi6C</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>mustapha suliman</t>
+          <t>micheler florian</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>rHQfYOz6</t>
+          <t>GtZAyRi8</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>mustapha suliman</t>
+          <t>geiger dennis</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>p6v39OGe</t>
+          <t>GdwP5bwG</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>srbeny dennis</t>
+          <t>bruun larsen jacob</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>vgFlmAm5</t>
+          <t>GdwP5bwG</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
         <is>
-          <t>giesselmann niko</t>
+          <t>bruun larsen jacob</t>
         </is>
       </c>
       <c r="DV4" t="inlineStr">
         <is>
-          <t>vgFlmAm5</t>
+          <t>0pNTmC8s</t>
         </is>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>giesselmann niko</t>
+          <t>prass alexander</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>SpbhoTNS</t>
+          <t>Asecu8a3</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>asta simon</t>
+          <t>tabakovic haris</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>A3uQrIzI</t>
+          <t>Asecu8a3</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>munz reno</t>
+          <t>tabakovic haris</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
         <is>
-          <t>A3uQrIzI</t>
+          <t>GOTDkA9I</t>
         </is>
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>munz reno</t>
+          <t>promel grischa</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>E1IiAd0j</t>
+          <t>WWSwmP1d</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>massimo roberto</t>
+          <t>hojlund oscar</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>48tkiDoS</t>
+          <t>APCymcXa</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>consbruch jomaine</t>
+          <t>lisztes krisztian</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>48tkiDoS</t>
+          <t>tbJx15yJ</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>consbruch jomaine</t>
+          <t>bebou ihlas</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>Kr5mFJ31</t>
+          <t>OrIOjLpG</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>hrgota branimir</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="inlineStr"/>
-      <c r="EN4" t="inlineStr"/>
-      <c r="EO4" t="inlineStr"/>
-      <c r="EP4" t="inlineStr"/>
-      <c r="EQ4" t="inlineStr"/>
-      <c r="ER4" t="inlineStr"/>
-      <c r="ES4" t="inlineStr"/>
-      <c r="ET4" t="inlineStr"/>
-      <c r="EU4" t="inlineStr"/>
-      <c r="EV4" t="inlineStr"/>
-      <c r="EW4" t="inlineStr"/>
-      <c r="EX4" t="inlineStr"/>
-      <c r="EY4" t="inlineStr"/>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>fRZB21nI</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>bischof tom</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>hljGyhNr</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>uzun can yilmaz</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>0xxsmCo1</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>collins nnamdi</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>0xxsmCo1</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>collins nnamdi</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>z9f8RgUQ</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>tuta</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr"/>
+      <c r="FA4" t="inlineStr"/>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>URX8dTEi</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>john marco</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>AF2Br9IA</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>jurasek david</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr"/>
+      <c r="FI4" t="inlineStr"/>
+      <c r="FJ4" t="inlineStr"/>
+      <c r="FK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6u6i5pie</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KvpRs0se</t>
+          <t>UJ1fQWzQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dedidis alexios</t>
+          <t>weiner timon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>K4vSNbp8</t>
+          <t>4lxZ6TzS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>butzen nils</t>
+          <t>johansson carl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>xMHywEPo</t>
+          <t>xfKprpfm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>el haija khalid</t>
+          <t>erras patrick</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>pGBzvY5j</t>
+          <t>Cr3vSdPM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>reddemann soren kurt</t>
+          <t>komenda marco</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>thNwIkl6</t>
+          <t>zi1rx9q2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>kramer paul</t>
+          <t>becker timo</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6o8fXpDt</t>
+          <t>pxVxwmy3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>schau justin</t>
+          <t>knudsen magnus</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>C0p6OSP4</t>
+          <t>EDemoJW7</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>gipson ken</t>
+          <t>holtby lewis</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6gJyXBrf</t>
+          <t>0Ah8TRF1</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>muqaj hamza</t>
+          <t>bernhardsson alexander</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0fU9OS9f</t>
+          <t>dbsIIrhi</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>richter joel</t>
+          <t>porath finn</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>YaHpiUBr</t>
+          <t>bmqSycbl</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>weinhauer erik</t>
+          <t>pichler benedikt</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>bZshci1p</t>
+          <t>lMBnrtYr</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>sezer cemal</t>
+          <t>machino shuto</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>tIXuiy4C</t>
+          <t>0MhuM4YL</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>kovar matej</t>
+          <t>grabara kamil</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dxkz9WG0</t>
+          <t>Aym7cCCj</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>arthur</t>
+          <t>fischer kilian</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>d4z5zQ7g</t>
+          <t>z58rzyyp</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>tapsoba edmond</t>
+          <t>bornauw sebastiaan</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2yf8EcuE</t>
+          <t>AZjCvCIn</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>tah jonathan</t>
+          <t>zesiger cedric</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>zog0NOeM</t>
+          <t>hbhnybaa</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>belocian jeanuel</t>
+          <t>kaminski jakub</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>QD7noPXB</t>
+          <t>pUChj7Xb</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>garcia aleix</t>
+          <t>arnold maximilian</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>zDjAwp82</t>
+          <t>AVMjVAqt</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>andrich robert</t>
+          <t>baku bote</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>QRtPmK69</t>
+          <t>444Jw1Mr</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>tella nathan</t>
+          <t>majer lovro</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>xvCz3Gwd</t>
+          <t>z522mgfh</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>hofmann jonas</t>
+          <t>svanberg mattias</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>82ETy0Me</t>
+          <t>WSswmxBa</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>adli amine</t>
+          <t>tiago tomas</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>WzQQSSfc</t>
+          <t>jsOwmeQB</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>schick patrik</t>
+          <t>wimmer patrick</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>ni9fEtMF</t>
+          <t>bTQKqpWl</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>hessel maxim</t>
+          <t>arp jann fiete</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>MiQRvA3I</t>
+          <t>Iu9wq1CJ</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>kampe paul</t>
+          <t>dahne thomas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>dKivR1Hu</t>
+          <t>hSeCNe90</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>liesegang marius</t>
+          <t>geschwill max</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>xAuZ1slR</t>
+          <t>Yitlr4Gb</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>prokopenko alexander</t>
+          <t>gigovic armin</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>SjjlN2Gj</t>
+          <t>MkuqZx07</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>seidemann kay</t>
+          <t>ivezic marko</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>WC2tydGd</t>
+          <t>lWfWDtt2</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>werner jannes</t>
+          <t>puchacz tymoteusz</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>xvqdoWXA</t>
+          <t>0btMY7wU</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>zank benjamin</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
+          <t>remberg nicolai</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>E7oeUFqn</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>rosenboom lasse</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>UXge5rm6</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>angely mathys</t>
+        </is>
+      </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>SjJ6pCvC</t>
+          <t>jmJ3jLRN</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>frimpong jeremie</t>
+          <t>behrens kevin</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>6cAIrW5Q</t>
+          <t>zgcECIjF</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>grimaldo alex</t>
+          <t>broger bennit</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2TTElOLP</t>
+          <t>21jDsx0f</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>hincapie pedro</t>
+          <t>dardai bence</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>fB4FKbSB</t>
+          <t>rZTSn6gr</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>lomb niklas</t>
+          <t>gerhardt yannick</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>nHOw5Jjn</t>
+          <t>OYbFR8ut</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>onyeka francis</t>
+          <t>muller marius</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>Wl6Cl3q8</t>
+          <t>ddHjOAgc</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>raterink othniel</t>
+          <t>odogu david</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>ldk7Wmoe</t>
+          <t>2sPPKXyd</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>stepanov artem</t>
+          <t>ozcan salih</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0Q5gjImi</t>
+          <t>Glknuas7</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>wirtz florian</t>
+          <t>wind jonas</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>QBHCDKff</t>
+          <t>hSeCNe90</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>xhaka granit</t>
+          <t>geschwill max</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>SjjlN2Gj</t>
+          <t>hSeCNe90</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>seidemann kay</t>
+          <t>geschwill max</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>SjjlN2Gj</t>
+          <t>Cr3vSdPM</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>seidemann kay</t>
+          <t>komenda marco</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0fU9OS9f</t>
+          <t>Yitlr4Gb</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>richter joel</t>
+          <t>gigovic armin</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>xvqdoWXA</t>
+          <t>Yitlr4Gb</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>zank benjamin</t>
+          <t>gigovic armin</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>xvqdoWXA</t>
+          <t>dbsIIrhi</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>zank benjamin</t>
+          <t>porath finn</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>bZshci1p</t>
+          <t>bTQKqpWl</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>sezer cemal</t>
+          <t>arp jann fiete</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>xAuZ1slR</t>
+          <t>bTQKqpWl</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>prokopenko alexander</t>
+          <t>arp jann fiete</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>xAuZ1slR</t>
+          <t>0Ah8TRF1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>prokopenko alexander</t>
+          <t>bernhardsson alexander</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>C0p6OSP4</t>
+          <t>0btMY7wU</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>gipson ken</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
+          <t>remberg nicolai</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>0btMY7wU</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>remberg nicolai</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>pxVxwmy3</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>knudsen magnus</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>2sPPKXyd</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>ozcan salih</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>2sPPKXyd</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>ozcan salih</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>444Jw1Mr</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>majer lovro</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>Glknuas7</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>wind jonas</t>
+        </is>
+      </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>6cAIrW5Q</t>
+          <t>Glknuas7</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>grimaldo alex</t>
+          <t>wind jonas</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>6cAIrW5Q</t>
+          <t>z522mgfh</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>grimaldo alex</t>
+          <t>svanberg mattias</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>dxkz9WG0</t>
+          <t>rZTSn6gr</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>arthur</t>
+          <t>gerhardt yannick</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>0Q5gjImi</t>
+          <t>rZTSn6gr</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>wirtz florian</t>
+          <t>gerhardt yannick</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>0Q5gjImi</t>
+          <t>WSswmxBa</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>wirtz florian</t>
+          <t>tiago tomas</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>82ETy0Me</t>
+          <t>21jDsx0f</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>adli amine</t>
+          <t>dardai bence</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>SjJ6pCvC</t>
+          <t>21jDsx0f</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>frimpong jeremie</t>
+          <t>dardai bence</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>SjJ6pCvC</t>
+          <t>AVMjVAqt</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>frimpong jeremie</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>QRtPmK69</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>tella nathan</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>QBHCDKff</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>xhaka granit</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>QBHCDKff</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>xhaka granit</t>
-        </is>
-      </c>
+          <t>baku bote</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>zDjAwp82</t>
+          <t>jaQQ0fMu</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>andrich robert</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr"/>
-      <c r="EG5" t="inlineStr"/>
-      <c r="EH5" t="inlineStr"/>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
-      <c r="EM5" t="inlineStr"/>
-      <c r="EN5" t="inlineStr"/>
-      <c r="EO5" t="inlineStr"/>
-      <c r="EP5" t="inlineStr"/>
-      <c r="EQ5" t="inlineStr"/>
-      <c r="ER5" t="inlineStr"/>
-      <c r="ES5" t="inlineStr"/>
-      <c r="ET5" t="inlineStr"/>
-      <c r="EU5" t="inlineStr"/>
-      <c r="EV5" t="inlineStr"/>
-      <c r="EW5" t="inlineStr"/>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>lla8DJW0</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>amoura mohamed</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>QscOyy8Q</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>maehle joakim</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>EFPPpPfD</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>schulz marvin</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>E7oeUFqn</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>rosenboom lasse</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>E7oeUFqn</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>rosenboom lasse</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>EDemoJW7</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>holtby lewis</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>EkcE3L0c</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>skrzybski steven</t>
+        </is>
+      </c>
       <c r="EX5" t="inlineStr"/>
       <c r="EY5" t="inlineStr"/>
+      <c r="EZ5" t="inlineStr"/>
+      <c r="FA5" t="inlineStr"/>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t>EqNGX6pE</t>
+        </is>
+      </c>
+      <c r="FI5" t="inlineStr">
+        <is>
+          <t>vranckx aster</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr"/>
+      <c r="FK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>W67CmLPh</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dEikH1Kb</t>
+          <t>Igk6vzlT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>behrens morten</t>
+          <t>nubel alexander</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GfxLwyRf</t>
+          <t>I9avdeat</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>schad dominik</t>
+          <t>stenzel pascal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COALarg5</t>
+          <t>QRcni8Si</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>frenkert lukas</t>
+          <t>chase anrie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>W629DD2p</t>
+          <t>f1kf4eiH</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>peatow torge</t>
+          <t>chabot julian</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2VV3mWal</t>
+          <t>x0JgoYBA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>kirkeskov mikkel</t>
+          <t>mittelstadt maximilian</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Gbu8HNXc</t>
+          <t>UTtpcjym</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>makridis charalampos</t>
+          <t>leweling jamie</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>joxYnHwl</t>
+          <t>zc2VFBzR</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>bazzoli luca</t>
+          <t>karazor atakan</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>tMs28wMD</t>
+          <t>0hF2GIXS</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>hendrix jorrit</t>
+          <t>stiller angelo</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>febm46cJ</t>
+          <t>bczcNJFB</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>lorenz marc</t>
+          <t>fuhrich chris</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>vqACZfUA</t>
+          <t>tnaRyr62</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>nemeth andras</t>
+          <t>millot enzo</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0jQoFve6</t>
+          <t>tUHAdtMH</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>grodowski joel</t>
+          <t>undav deniz</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Igk6vzlT</t>
+          <t>0E4pecgh</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>nubel alexander</t>
+          <t>zentner robin</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>jHU6p6gQ</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>kohr dominik</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>EilL1urA</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>bell stefan</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ru11TuPI</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>hanche olsen andreas</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>rsCh6sgU</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>caci anthony</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>v13GHQFg</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sano kaishu</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>b3H5VR8I</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>amiri nadiem</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>troQho4L</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>mwene philipp</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>tYFvyfg2</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>hong hyun seok</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>try8xret</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>lee jae sung</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>MicyKu3h</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>burkardt jonathan</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>MTjX2S5c</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>bredlow fabian</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>dIsZ5Eyb</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>demirovic ermedin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>x2tZQYZD</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>hendriks ramon</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>hYP3hnMa</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>kratzig frans</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>GQOPPSgM</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>rieder fabian</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>O28yXBfT</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>toure el bilal</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>MNTqORR3</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>vagnoman josha</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>tdKD2AnM</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>barkok aymen</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>U7l59rXJ</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>da costa danny</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>YZpfvGBa</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>leitsch maxim</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>jRexguuN</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>nebel paul</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>lnXQSLq2</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>onisiwo karim</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>lIpGNEb4</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>riess lasse</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>jyZ4c9ao</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>sieb armindo</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>xWOAn3v6</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>veratschnig nikolas</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>rZFtbGem</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>widmer silvan</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>GQOPPSgM</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>rieder fabian</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>GQOPPSgM</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>rieder fabian</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>bczcNJFB</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>fuhrich chris</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>MNTqORR3</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>vagnoman josha</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>MNTqORR3</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>vagnoman josha</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
           <t>I9avdeat</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>stenzel pascal</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>QRcni8Si</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>chase anrie</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>f1kf4eiH</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>chabot julian</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>x0JgoYBA</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>mittelstadt maximilian</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>GQOPPSgM</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>rieder fabian</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>zc2VFBzR</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>karazor atakan</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>0hF2GIXS</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>stiller angelo</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>bczcNJFB</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>fuhrich chris</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>4YDUd1at</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>woltemade nick</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>dIsZ5Eyb</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>demirovic ermedin</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>OEtg0Exj</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>amenyido etienne</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>b5ojgUKT</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>bolay luca</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>hAYcztZo</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>deters thorben</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>SMR74iXq</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>kyerewaa daniel</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>GdTT8aB4</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>mees joshua</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>tWjSYhMg</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>preissinger rico</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>xbHTqKPs</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>schenk johannes</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0AIlcS72</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>scherder simon</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>pC5Aa7Fa</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>ter horst jano</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>MTjX2S5c</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>bredlow fabian</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>tSVfwjYd</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>diehl justin</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>x2tZQYZD</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>hendriks ramon</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>bXYV35NK</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>keitel yannik</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>hYP3hnMa</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>kratzig frans</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>dIsZ5Eyb</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>demirovic ermedin</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>tUHAdtMH</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>undav deniz</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>O28yXBfT</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>toure el bilal</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>O28yXBfT</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>toure el bilal</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
         <is>
           <t>UTtpcjym</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>leweling jamie</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>tnaRyr62</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>millot enzo</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>SIml2Qes</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>silas</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>tUHAdtMH</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>undav deniz</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>SMR74iXq</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>kyerewaa daniel</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>SMR74iXq</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>kyerewaa daniel</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>febm46cJ</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>lorenz marc</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>tWjSYhMg</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>preissinger rico</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>tWjSYhMg</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>preissinger rico</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>joxYnHwl</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>bazzoli luca</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>GdTT8aB4</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>mees joshua</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>GdTT8aB4</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>mees joshua</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>tMs28wMD</t>
-        </is>
-      </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>hendrix jorrit</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>OEtg0Exj</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>amenyido etienne</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>OEtg0Exj</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>amenyido etienne</t>
-        </is>
-      </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>vqACZfUA</t>
+          <t>YZpfvGBa</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>nemeth andras</t>
+          <t>leitsch maxim</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>b5ojgUKT</t>
+          <t>YZpfvGBa</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
-          <t>bolay luca</t>
+          <t>leitsch maxim</t>
         </is>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>b5ojgUKT</t>
+          <t>EilL1urA</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>bolay luca</t>
+          <t>bell stefan</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
         <is>
-          <t>0jQoFve6</t>
+          <t>jyZ4c9ao</t>
         </is>
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>grodowski joel</t>
+          <t>sieb armindo</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>hYP3hnMa</t>
+          <t>jyZ4c9ao</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
         <is>
-          <t>kratzig frans</t>
+          <t>sieb armindo</t>
         </is>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>hYP3hnMa</t>
+          <t>tYFvyfg2</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>kratzig frans</t>
+          <t>hong hyun seok</t>
         </is>
       </c>
       <c r="DL6" t="inlineStr">
         <is>
-          <t>x0JgoYBA</t>
+          <t>rZFtbGem</t>
         </is>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>mittelstadt maximilian</t>
+          <t>widmer silvan</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>tUHAdtMH</t>
+          <t>rZFtbGem</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>undav deniz</t>
+          <t>widmer silvan</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>tUHAdtMH</t>
+          <t>rsCh6sgU</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>undav deniz</t>
+          <t>caci anthony</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
         <is>
-          <t>dIsZ5Eyb</t>
+          <t>tdKD2AnM</t>
         </is>
       </c>
       <c r="DS6" t="inlineStr">
         <is>
-          <t>demirovic ermedin</t>
+          <t>barkok aymen</t>
         </is>
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>UTtpcjym</t>
+          <t>tdKD2AnM</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
         <is>
-          <t>leweling jamie</t>
+          <t>barkok aymen</t>
         </is>
       </c>
       <c r="DV6" t="inlineStr">
         <is>
-          <t>UTtpcjym</t>
+          <t>b3H5VR8I</t>
         </is>
       </c>
       <c r="DW6" t="inlineStr">
         <is>
-          <t>leweling jamie</t>
+          <t>amiri nadiem</t>
         </is>
       </c>
       <c r="DX6" t="inlineStr">
         <is>
-          <t>bczcNJFB</t>
+          <t>xWOAn3v6</t>
         </is>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>fuhrich chris</t>
+          <t>veratschnig nikolas</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>x2tZQYZD</t>
+          <t>xWOAn3v6</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>hendriks ramon</t>
+          <t>veratschnig nikolas</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>x2tZQYZD</t>
+          <t>try8xret</t>
         </is>
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>hendriks ramon</t>
+          <t>lee jae sung</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>I9avdeat</t>
+          <t>63mrBJnS</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>stenzel pascal</t>
+          <t>al dakhil ameen</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>tSVfwjYd</t>
+          <t>ja18uZOO</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>diehl justin</t>
+          <t>nartey nikolas</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>tSVfwjYd</t>
+          <t>pIMPjP8B</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>diehl justin</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>GQOPPSgM</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>rieder fabian</t>
-        </is>
-      </c>
+          <t>jenz moritz</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr"/>
+      <c r="EK6" t="inlineStr"/>
       <c r="EL6" t="inlineStr"/>
       <c r="EM6" t="inlineStr"/>
-      <c r="EN6" t="inlineStr"/>
-      <c r="EO6" t="inlineStr"/>
-      <c r="EP6" t="inlineStr"/>
-      <c r="EQ6" t="inlineStr"/>
-      <c r="ER6" t="inlineStr"/>
-      <c r="ES6" t="inlineStr"/>
-      <c r="ET6" t="inlineStr"/>
-      <c r="EU6" t="inlineStr"/>
-      <c r="EV6" t="inlineStr"/>
-      <c r="EW6" t="inlineStr"/>
-      <c r="EX6" t="inlineStr"/>
-      <c r="EY6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>4YDUd1at</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>woltemade nick</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>x2tZQYZD</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>hendriks ramon</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>x2tZQYZD</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>hendriks ramon</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>x0JgoYBA</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>mittelstadt maximilian</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>hCWLxEzr</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>rouault anthony</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr"/>
+      <c r="FC6" t="inlineStr"/>
+      <c r="FD6" t="inlineStr"/>
+      <c r="FE6" t="inlineStr"/>
+      <c r="FF6" t="inlineStr"/>
+      <c r="FG6" t="inlineStr"/>
+      <c r="FH6" t="inlineStr"/>
+      <c r="FI6" t="inlineStr"/>
+      <c r="FJ6" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="FK6" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ATsadFmo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>zetterer michael</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>xQzNNXkj</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>stark niklas</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>jacFHyR9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>friedl marco</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>xjjdBYsc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>jung anthony</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>tYnkajw9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>weiser mitchell</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hIljeTIQ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lynen senne</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>jJ1sdqU7</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>stage jens</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>bDdYUcr2</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>agu felix</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>lGA7E78J</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>schmid romano</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>8McNJcKC</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>ducksch marvin</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>MkHz7wta</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>gideon justin</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>xlBg2ttC</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>kobel gregor</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>8nv0ZZYK</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>ryerson julian</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>b3gqj94D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>anton waldemar</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>G43Lp4in</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>sule niklas</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>hKLN8mA7</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>schlotterbeck nico</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>YJu3hSpk</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>can emre</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>trpxfbO3</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>gross pascal</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>8UkK3Y37</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>sabitzer marcel</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>hW5Goyrc</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>brandt julian</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>zmDkHahi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>bynoe gittens jamie</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>6PhlgcmU</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>beier maximilian</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>WlEZExcF</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>alvero skelly</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>AquFxJsn</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>backhaus mio</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>UNvXGPqn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>bittencourt leonardo</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>lbqsZvEf</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>burke oliver</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2FUXXkKc</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>deman olivier</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>46r3Wu9b</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>hansen aaroen isak</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>hG2tW3OE</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>malatini julian</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>jag6GVQG</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>bensebaini ramy</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>G8jmgFZE</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>duranville julien</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>phuSePi7</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>lotka marcel</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>KOdKXsao</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>malen donyell</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>WzJWzU9r</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>mane filippo</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0QYpaRhf</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>meyer alexander</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>80RErj9O</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>nmecha felix</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>S6I8rZWk</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>topp keke</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>S6I8rZWk</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>topp keke</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>MkHz7wta</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>gideon justin</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>8McNJcKC</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>ducksch marvin</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>jag6GVQG</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>bensebaini ramy</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>jag6GVQG</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>bensebaini ramy</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>G43Lp4in</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>sule niklas</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>zmDkHahi</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>bynoe gittens jamie</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>KOdKXsao</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>malen donyell</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>KOdKXsao</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>malen donyell</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>6PhlgcmU</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>beier maximilian</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>80RErj9O</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>nmecha felix</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>80RErj9O</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>nmecha felix</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>hW5Goyrc</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>brandt julian</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>4pESGQSm</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>pieper amos</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>fVyb9zlg</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>couto yan</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>YXRCmup6</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>guirassy serhou</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>Umh5qbVs</t>
+        </is>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>watjen kjell</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t>S6I8rZWk</t>
+        </is>
+      </c>
+      <c r="EO7" t="inlineStr">
+        <is>
+          <t>topp keke</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>E7uclPCf</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>veljkovic milos</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr"/>
+      <c r="EY7" t="inlineStr"/>
+      <c r="EZ7" t="inlineStr"/>
+      <c r="FA7" t="inlineStr"/>
+      <c r="FB7" t="inlineStr"/>
+      <c r="FC7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
+      <c r="FF7" t="inlineStr"/>
+      <c r="FG7" t="inlineStr"/>
+      <c r="FH7" t="inlineStr"/>
+      <c r="FI7" t="inlineStr"/>
+      <c r="FJ7" t="inlineStr"/>
+      <c r="FK7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jLJDHgod</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>d0rCJ6XA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>krahl julian</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dQ9SqUtk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>toure almamy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EecfGnDI</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tomiak boris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0fO4CaGi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>heuer jannis</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>j3uLBTA8</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ritter marlon</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2mMIA66I</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>kaloc filip</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>8d13nxU4</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>wekesser erik</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>tddjZy0T</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>klement phillipp</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>vsimiktN</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>opoku aaron</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>843k6G9D</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>hanslik daniel</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>tbbK5T30</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>ernst tjark</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Slhuy0y3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>kenny jonjoe</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>A5MUk7uC</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>gechter linus</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>4fsvgxKi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>dardai marton</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>A7bJsd2S</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>zeefuik deyoraiso</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>fZjqy5kN</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>karbownik michal</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>6XydaRuI</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>demme diego</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>zPa6aAD8</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>maza ibrahim</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>QNd9XJHR</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>cuisance mickael</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>fwLe2Csr</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>schuler luca</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>jRG1UH32</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>scherhant derry</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>lnwXQmIl</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>ache ragnar</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>YyIyM2ke</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>elvedi jan</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>rwtqk3Wo</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>kleinhansl florian</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0EtdioIN</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>redondo kenny</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>CdGwhV3n</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>spahic avdo</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>WYIHibUi</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>tachie richmond</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Igz4CtLA</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>christensen gustav</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>hWXQwRg8</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>dardai palko</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>pWc1VLFr</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>gersbeck marius</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>z1kXPVQh</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>klemens pascal</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>MkyFE8Cj</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>leistner toni</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>txGA3Xvc</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>niederlechner florian</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>bVNfLx3q</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>prevljak smail</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>xnfqsDHU</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>thorsteinsson jon dagur</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>G6KuK9GH</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>winkler marten</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0EtdioIN</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>redondo kenny</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>0EtdioIN</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>redondo kenny</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>tddjZy0T</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>klement phillipp</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>YyIyM2ke</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>elvedi jan</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>YyIyM2ke</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>elvedi jan</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>jozCYOMc</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>gyamerah jan</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>lnwXQmIl</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>ache ragnar</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>lnwXQmIl</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>ache ragnar</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>vsimiktN</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>opoku aaron</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>WAGLIfPd</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>mause jannik</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>8d13nxU4</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>wekesser erik</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>xnfqsDHU</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>thorsteinsson jon dagur</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>xnfqsDHU</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>thorsteinsson jon dagur</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>fwLe2Csr</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>schuler luca</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>z1kXPVQh</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>klemens pascal</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>z1kXPVQh</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>klemens pascal</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>6XydaRuI</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>demme diego</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>G6KuK9GH</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>winkler marten</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>G6KuK9GH</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>winkler marten</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>fZjqy5kN</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>karbownik michal</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>txGA3Xvc</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>niederlechner florian</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>txGA3Xvc</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>niederlechner florian</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>jRG1UH32</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>scherhant derry</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>MkyFE8Cj</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>leistner toni</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>MkyFE8Cj</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>leistner toni</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>zPa6aAD8</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>maza ibrahim</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr">
+        <is>
+          <t>lIkG4xvp</t>
+        </is>
+      </c>
+      <c r="EO8" t="inlineStr">
+        <is>
+          <t>zimmer jean</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>0dT23r7q</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>raschl tobias</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>843k6G9D</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>hanslik daniel</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr"/>
+      <c r="EW8" t="inlineStr"/>
+      <c r="EX8" t="inlineStr"/>
+      <c r="EY8" t="inlineStr"/>
+      <c r="EZ8" t="inlineStr"/>
+      <c r="FA8" t="inlineStr"/>
+      <c r="FB8" t="inlineStr"/>
+      <c r="FC8" t="inlineStr"/>
+      <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>A33XyOWA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kz0IYO5q</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kristof nicolas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sr0pRlmi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>baum elias</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CADMRt26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pinckert lukas</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>nkVANHYO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>le joncour florian</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>MmRiKDc4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>neubauer maurice</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8S91z1hc</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>feil manuel</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UN7i7Cf3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>fellhauer robin</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>bN5KbyQf</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>sahin semih</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>rJzmNH08</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>damar muhammed</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>IsoKFb9C</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>asllani fisnik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>CSvc98Io</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>schnellbacher luca pascal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dOWuRZlo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>schuhen marcel</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>E9apS1Bg</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>riedel clemens</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>80E6DP7t</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>muller andreas</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>MVVlcIlh</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>vukotic aleksandar</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>nFpZ4rdg</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>bader matthias</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>GbIogcRb</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>klefisch kai</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rZoUaqpe</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>will paul</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>QHwCPXNM</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>nurnberger fabian</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>WrbMSCIj</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>lidberg isac</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>GQxCf7Bi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>corredor killian</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>hAGrRnhD</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>lakenmacher fynn</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>WSuIj5OD</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>boss tim</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>CrYn57el</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>mahmoud mohammad</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>lWlv74vQ</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>petkov lukas</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>zL8TcKhL</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>rohr maximilian</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>fHsspqLg</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>sicker arne</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>fcnB8yqG</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>bueno guillermo</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>bDFC7UGu</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>el idrissi othmane</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>4ttlRMFN</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>hornby fraser</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>2wOM3Nuj</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>kempe tobias</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>6VRnUvLl</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>lopez sergio</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>EBWgEtZc</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>maglica matej</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>O2dfXz1S</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>marseiler luca</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>x8LSZTrk</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>niemczycki karol</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0zdchsQJ</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>papela merveille</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>vZBhb9vk</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>gerezgiher filimon</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>CSvc98Io</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>schnellbacher luca pascal</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>lWlv74vQ</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>petkov lukas</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>lWlv74vQ</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>petkov lukas</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>8S91z1hc</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>feil manuel</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>rqmHR01A</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>sickinger carlo</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>UN7i7Cf3</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>fellhauer robin</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>vqV83aMf</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>schmahl frederik</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>nkVANHYO</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>le joncour florian</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>O2dfXz1S</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>marseiler luca</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>O2dfXz1S</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>marseiler luca</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>80E6DP7t</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>muller andreas</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>fcnB8yqG</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>bueno guillermo</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>fcnB8yqG</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>bueno guillermo</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>QHwCPXNM</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>nurnberger fabian</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>6VRnUvLl</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>lopez sergio</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>6VRnUvLl</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>lopez sergio</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>nFpZ4rdg</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>bader matthias</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>0zdchsQJ</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>papela merveille</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>0zdchsQJ</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>papela merveille</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>GbIogcRb</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>klefisch kai</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>EBWgEtZc</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>maglica matej</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>EBWgEtZc</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>maglica matej</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>WrbMSCIj</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>lidberg isac</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>Kv8zt49I</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>stock paul</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>zL8TcKhL</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>rohr maximilian</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
+          <t>zL8TcKhL</t>
+        </is>
+      </c>
+      <c r="ES9" t="inlineStr">
+        <is>
+          <t>rohr maximilian</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t>rJzmNH08</t>
+        </is>
+      </c>
+      <c r="EU9" t="inlineStr">
+        <is>
+          <t>damar muhammed</t>
+        </is>
+      </c>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="inlineStr"/>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0Ug8yfLU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mcx5TeXa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>heuer fernandes daniel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>bPpZBqLi</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hefti silvan</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jV3UcfqE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hadzikadunic dennis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6LrWuvC1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>elfadli daniel</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bympdcHJ</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>muheim miro</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MRT6G9pQ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>meffert jonas</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SClyr2eG</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>karabec adam</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>WQz3HTDf</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>pherai manuel</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>OIB9EK1N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>balde fabio</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>SKtwDNsR</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>glatzel robert nesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SllmjqTg</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>konigsdorffer ransford</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>xbHTqKPs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>schenk johannes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>pC5Aa7Fa</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>ter horst jano</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>W629DD2p</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>peatow torge</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>COALarg5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>frenkert lukas</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2VV3mWal</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>kirkeskov mikkel</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>tMs28wMD</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>hendrix jorrit</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>joxYnHwl</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>bazzoli luca</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>GdTT8aB4</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>mees joshua</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>febm46cJ</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>lorenz marc</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0jQoFve6</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>grodowski joel</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>IJvNR7LH</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>heyer moritz</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>UBu3UwYC</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>katterbach noah</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>r7AcmFSk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>mickel tom</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>xULqadCe</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>kisilowski nicolas</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>ptaUIS22</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>poreba lukasz</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>UcheHrHf</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>ramos guilherme</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>Kf9h2WGQ</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>reis ludovit</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>IaM1bKAQ</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>richter marco</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>dEikH1Kb</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>behrens morten</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>b5ojgUKT</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>bolay luca</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>hAYcztZo</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>deters thorben</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Ik1ykn3o</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>koulis niko</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>vqACZfUA</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>nemeth andras</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>0AIlcS72</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>scherder simon</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>Kf9h2WGQ</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>reis ludovit</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>Kf9h2WGQ</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>reis ludovit</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>WQz3HTDf</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>pherai manuel</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>IJvNR7LH</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>heyer moritz</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>IJvNR7LH</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>heyer moritz</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>6LrWuvC1</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>elfadli daniel</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>E7JLI2DO</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>selke davie</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>E7JLI2DO</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>selke davie</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>SKtwDNsR</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>glatzel robert nesta</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>IaM1bKAQ</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>richter marco</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>IaM1bKAQ</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>richter marco</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>OIB9EK1N</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>balde fabio</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>SMR74iXq</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>kyerewaa daniel</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>GdTT8aB4</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>mees joshua</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>Gbu8HNXc</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>makridis charalampos</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>febm46cJ</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>lorenz marc</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>vqACZfUA</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>nemeth andras</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>vqACZfUA</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>nemeth andras</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>OEtg0Exj</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>amenyido etienne</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>tWjSYhMg</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>preissinger rico</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>tMs28wMD</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>hendrix jorrit</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>hAYcztZo</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>deters thorben</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>hAYcztZo</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>deters thorben</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>0jQoFve6</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>grodowski joel</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr"/>
+      <c r="EE10" t="inlineStr"/>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr"/>
+      <c r="EH10" t="inlineStr"/>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
+      <c r="EM10" t="inlineStr"/>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t>E7JLI2DO</t>
+        </is>
+      </c>
+      <c r="EO10" t="inlineStr">
+        <is>
+          <t>selke davie</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t>ptaUIS22</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>poreba lukasz</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr">
+        <is>
+          <t>ptaUIS22</t>
+        </is>
+      </c>
+      <c r="ES10" t="inlineStr">
+        <is>
+          <t>poreba lukasz</t>
+        </is>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t>SClyr2eG</t>
+        </is>
+      </c>
+      <c r="EU10" t="inlineStr">
+        <is>
+          <t>karabec adam</t>
+        </is>
+      </c>
+      <c r="EV10" t="inlineStr"/>
+      <c r="EW10" t="inlineStr"/>
+      <c r="EX10" t="inlineStr"/>
+      <c r="EY10" t="inlineStr"/>
+      <c r="EZ10" t="inlineStr"/>
+      <c r="FA10" t="inlineStr"/>
+      <c r="FB10" t="inlineStr"/>
+      <c r="FC10" t="inlineStr"/>
+      <c r="FD10" t="inlineStr"/>
+      <c r="FE10" t="inlineStr"/>
+      <c r="FF10" t="inlineStr"/>
+      <c r="FG10" t="inlineStr"/>
+      <c r="FH10" t="inlineStr"/>
+      <c r="FI10" t="inlineStr"/>
+      <c r="FJ10" t="inlineStr"/>
+      <c r="FK10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fgQ4JFGq</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bylmonK5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>reichert jan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dMPYlirB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>rose villadsen oliver</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AaXC2DTB</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>knoche robin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4GFyNBT2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>jeltsch finn</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Y1uqqiIe</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>soares danilo</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>YXX9uBO9</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>justvan julian</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>hnqDstcS</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>castrop jens</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>I1JWh0I4</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>flick florian</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>zsLgxeCo</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>jander caspar</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>lURc3Lpo</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>pick florian</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>rHUQL532</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>schleimer lukas</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dWQIRGp0</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>reimann dominik</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>nT3WIdHQ</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>hugonet jean</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>EsnjdRBb</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>mathisen marcus</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>dClubWya</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>heber daniel</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>xA8O15U4</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>musonda lubambo</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>fH72vUIc</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>gnaka silas</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Kr4UWDeF</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>omer el zein abu bekir</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>SzPX3jyU</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>el hankouri mo</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>MolPXmrg</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>ceka jason</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>xnYgdAQ0</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>kaars martijn</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>4dIJUitM</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>amaechi xavier</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>YsfI5FfH</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>janisch tim</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>razRw7r9</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>joachims simon</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0jthSqAB</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>kukucka michal</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>fRViBeZ4</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>lubach rafael</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>YeWnSuDP</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>okunuki kanji</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>UNcy9ySd</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>sevcik michal</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>UgcDv2mo</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>burcu livan</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>IiYd3b4I</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>hercher philipp</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>A9kiVOrq</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>hoti andi</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>EkMrawol</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>ito tatsuya</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>pEQYX0TC</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>krempicki connor</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>QLxRGC6m</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>kruth noah</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>nLuvpPGf</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>michel falko</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>4vJQvilJ</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>nollenberger alexander</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>hjh8FYxE</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>teixera bryan</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>YsfI5FfH</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>janisch tim</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>YsfI5FfH</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>janisch tim</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>lURc3Lpo</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>pick florian</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>UNcy9ySd</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>sevcik michal</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>UNcy9ySd</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>sevcik michal</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>YXX9uBO9</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>justvan julian</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>fRViBeZ4</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>lubach rafael</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>fRViBeZ4</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>lubach rafael</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>zsLgxeCo</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>jander caspar</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>xn1K9Ep6</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>tzimas stefanos</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>hnqDstcS</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>castrop jens</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>UgcDv2mo</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>burcu livan</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>UgcDv2mo</t>
+        </is>
+      </c>
+      <c r="DC11" t="inlineStr">
+        <is>
+          <t>burcu livan</t>
+        </is>
+      </c>
+      <c r="DD11" t="inlineStr">
+        <is>
+          <t>MolPXmrg</t>
+        </is>
+      </c>
+      <c r="DE11" t="inlineStr">
+        <is>
+          <t>ceka jason</t>
+        </is>
+      </c>
+      <c r="DF11" t="inlineStr">
+        <is>
+          <t>pEQYX0TC</t>
+        </is>
+      </c>
+      <c r="DG11" t="inlineStr">
+        <is>
+          <t>krempicki connor</t>
+        </is>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>pEQYX0TC</t>
+        </is>
+      </c>
+      <c r="DI11" t="inlineStr">
+        <is>
+          <t>krempicki connor</t>
+        </is>
+      </c>
+      <c r="DJ11" t="inlineStr">
+        <is>
+          <t>Kr4UWDeF</t>
+        </is>
+      </c>
+      <c r="DK11" t="inlineStr">
+        <is>
+          <t>omer el zein abu bekir</t>
+        </is>
+      </c>
+      <c r="DL11" t="inlineStr">
+        <is>
+          <t>4vJQvilJ</t>
+        </is>
+      </c>
+      <c r="DM11" t="inlineStr">
+        <is>
+          <t>nollenberger alexander</t>
+        </is>
+      </c>
+      <c r="DN11" t="inlineStr">
+        <is>
+          <t>4vJQvilJ</t>
+        </is>
+      </c>
+      <c r="DO11" t="inlineStr">
+        <is>
+          <t>nollenberger alexander</t>
+        </is>
+      </c>
+      <c r="DP11" t="inlineStr">
+        <is>
+          <t>4dIJUitM</t>
+        </is>
+      </c>
+      <c r="DQ11" t="inlineStr">
+        <is>
+          <t>amaechi xavier</t>
+        </is>
+      </c>
+      <c r="DR11" t="inlineStr">
+        <is>
+          <t>nLuvpPGf</t>
+        </is>
+      </c>
+      <c r="DS11" t="inlineStr">
+        <is>
+          <t>michel falko</t>
+        </is>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>nLuvpPGf</t>
+        </is>
+      </c>
+      <c r="DU11" t="inlineStr">
+        <is>
+          <t>michel falko</t>
+        </is>
+      </c>
+      <c r="DV11" t="inlineStr">
+        <is>
+          <t>fH72vUIc</t>
+        </is>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>gnaka silas</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>IiYd3b4I</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>hercher philipp</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>IiYd3b4I</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>hercher philipp</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>SzPX3jyU</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>el hankouri mo</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr"/>
+      <c r="EE11" t="inlineStr"/>
+      <c r="EF11" t="inlineStr"/>
+      <c r="EG11" t="inlineStr"/>
+      <c r="EH11" t="inlineStr"/>
+      <c r="EI11" t="inlineStr"/>
+      <c r="EJ11" t="inlineStr"/>
+      <c r="EK11" t="inlineStr"/>
+      <c r="EL11" t="inlineStr"/>
+      <c r="EM11" t="inlineStr"/>
+      <c r="EN11" t="inlineStr">
+        <is>
+          <t>dhZeCRHq</t>
+        </is>
+      </c>
+      <c r="EO11" t="inlineStr">
+        <is>
+          <t>yilmaz berkay</t>
+        </is>
+      </c>
+      <c r="EP11" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="EQ11" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="ER11" t="inlineStr">
+        <is>
+          <t>xxMuA1lC</t>
+        </is>
+      </c>
+      <c r="ES11" t="inlineStr">
+        <is>
+          <t>karafiat ondrej</t>
+        </is>
+      </c>
+      <c r="ET11" t="inlineStr">
+        <is>
+          <t>4GFyNBT2</t>
+        </is>
+      </c>
+      <c r="EU11" t="inlineStr">
+        <is>
+          <t>jeltsch finn</t>
+        </is>
+      </c>
+      <c r="EV11" t="inlineStr"/>
+      <c r="EW11" t="inlineStr"/>
+      <c r="EX11" t="inlineStr"/>
+      <c r="EY11" t="inlineStr"/>
+      <c r="EZ11" t="inlineStr"/>
+      <c r="FA11" t="inlineStr"/>
+      <c r="FB11" t="inlineStr"/>
+      <c r="FC11" t="inlineStr"/>
+      <c r="FD11" t="inlineStr"/>
+      <c r="FE11" t="inlineStr"/>
+      <c r="FF11" t="inlineStr"/>
+      <c r="FG11" t="inlineStr"/>
+      <c r="FH11" t="inlineStr"/>
+      <c r="FI11" t="inlineStr"/>
+      <c r="FJ11" t="inlineStr"/>
+      <c r="FK11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
